--- a/outputs/alignment-warnings.xlsx
+++ b/outputs/alignment-warnings.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4035,14 +4035,14 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4062,14 +4062,14 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4170,14 +4170,14 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4251,14 +4251,14 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4278,14 +4278,14 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4305,14 +4305,14 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4467,14 +4467,14 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4548,14 +4548,14 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4602,14 +4602,14 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4629,14 +4629,14 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4683,14 +4683,14 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4737,14 +4737,14 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role S in language: kala1400, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5304,14 +5304,14 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role S in language: kala1400, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8193,14 +8193,14 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8220,14 +8220,14 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8247,14 +8247,14 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -8301,14 +8301,14 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8409,14 +8409,14 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8436,14 +8436,14 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8463,14 +8463,14 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8490,14 +8490,14 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8517,14 +8517,14 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8544,14 +8544,14 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -8625,14 +8625,14 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8733,14 +8733,14 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8760,14 +8760,14 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8787,14 +8787,14 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-spec and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-spec and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10765,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -10785,14 +10785,14 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10812,14 +10812,14 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10839,14 +10839,14 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10866,14 +10866,14 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10893,14 +10893,14 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10920,14 +10920,14 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -10947,14 +10947,14 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12108,7 +12108,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13620,7 +13620,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13944,7 +13944,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13971,7 +13971,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14133,7 +14133,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14160,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14376,7 +14376,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14457,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14673,7 +14673,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14808,7 +14808,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -16408,7 +16408,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16462,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -16482,14 +16482,14 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16543,7 +16543,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3fobv-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3fobv-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3fobv-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3fobv-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16887,14 +16887,14 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -16914,14 +16914,14 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -16941,14 +16941,14 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16995,14 +16995,14 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -17022,14 +17022,14 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17589,7 +17589,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17616,7 +17616,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17751,7 +17751,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17778,7 +17778,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17913,7 +17913,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18210,7 +18210,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18831,7 +18831,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18885,7 +18885,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18912,7 +18912,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18966,7 +18966,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18993,7 +18993,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19074,14 +19074,14 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -19101,7 +19101,7 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19135,7 +19135,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -19155,14 +19155,14 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19216,7 +19216,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19290,7 +19290,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19803,7 +19803,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19911,7 +19911,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20019,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20073,7 +20073,7 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20181,7 +20181,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20424,7 +20424,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20586,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20721,7 +20721,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21133,7 +21133,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -21153,14 +21153,14 @@
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -21180,14 +21180,14 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -21241,7 +21241,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -21261,7 +21261,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21288,7 +21288,7 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21342,7 +21342,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21396,14 +21396,14 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -21423,7 +21423,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21558,7 +21558,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21720,7 +21720,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21747,7 +21747,7 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22206,7 +22206,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22287,7 +22287,7 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -22503,14 +22503,14 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -22530,7 +22530,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22584,14 +22584,14 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22638,14 +22638,14 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -22665,14 +22665,14 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -22746,14 +22746,14 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -22773,7 +22773,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -22800,14 +22800,14 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -22827,14 +22827,14 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -22854,14 +22854,14 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22935,14 +22935,14 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22989,14 +22989,14 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -23016,14 +23016,14 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -23097,14 +23097,14 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -23124,7 +23124,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -23151,14 +23151,14 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23988,7 +23988,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24015,7 +24015,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24042,7 +24042,7 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24069,7 +24069,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24501,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24582,7 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24636,7 +24636,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24690,7 +24690,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24744,7 +24744,7 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24825,7 +24825,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24852,7 +24852,7 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24906,7 +24906,7 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24933,7 +24933,7 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24960,7 +24960,7 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25365,7 +25365,7 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25392,7 +25392,7 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25446,7 +25446,7 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25500,7 +25500,7 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25608,7 +25608,7 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26094,7 +26094,7 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26148,7 +26148,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26256,7 +26256,7 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26337,7 +26337,7 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26688,7 +26688,7 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26796,7 +26796,7 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26850,7 +26850,7 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26877,7 +26877,7 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26904,7 +26904,7 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27012,7 +27012,7 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27066,7 +27066,7 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27120,7 +27120,7 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27174,7 +27174,7 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27228,7 +27228,7 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27282,7 +27282,7 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27390,7 +27390,7 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27417,7 +27417,7 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27444,7 +27444,7 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27498,7 +27498,7 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27606,7 +27606,7 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27633,7 +27633,7 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27714,7 +27714,7 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27768,7 +27768,7 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27930,7 +27930,7 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27957,7 +27957,7 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28038,7 +28038,7 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28065,7 +28065,7 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28092,7 +28092,7 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28146,7 +28146,7 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28173,7 +28173,7 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28200,7 +28200,7 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28308,7 +28308,7 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28362,7 +28362,7 @@
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28389,7 +28389,7 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28470,7 +28470,7 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28578,7 +28578,7 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28605,7 +28605,7 @@
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29253,7 +29253,7 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29334,7 +29334,7 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30090,7 +30090,7 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30117,7 +30117,7 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30144,7 +30144,7 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30225,7 +30225,7 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30333,7 +30333,7 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30360,7 +30360,7 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30522,7 +30522,7 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30576,7 +30576,7 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30630,7 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30657,7 +30657,7 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30792,7 +30792,7 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30846,7 +30846,7 @@
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30873,7 +30873,7 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30900,7 +30900,7 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31440,7 +31440,7 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31494,7 +31494,7 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31521,7 +31521,7 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31548,7 +31548,7 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31602,7 +31602,7 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31629,7 +31629,7 @@
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31656,7 +31656,7 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31845,7 +31845,7 @@
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31872,7 +31872,7 @@
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31926,7 +31926,7 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31953,7 +31953,7 @@
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32466,7 +32466,7 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32520,7 +32520,7 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32574,7 +32574,7 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32601,7 +32601,7 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32628,7 +32628,7 @@
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="E1195" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="E1196" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="E1197" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32763,7 +32763,7 @@
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32790,7 +32790,7 @@
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32844,7 +32844,7 @@
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32871,7 +32871,7 @@
       </c>
       <c r="E1202" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32898,7 +32898,7 @@
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32925,7 +32925,7 @@
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="E1205" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32979,7 +32979,7 @@
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="E1207" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33033,7 +33033,7 @@
       </c>
       <c r="E1208" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33060,7 +33060,7 @@
       </c>
       <c r="E1209" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33087,7 +33087,7 @@
       </c>
       <c r="E1210" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33114,7 +33114,7 @@
       </c>
       <c r="E1211" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33141,7 +33141,7 @@
       </c>
       <c r="E1212" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33168,7 +33168,7 @@
       </c>
       <c r="E1213" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33195,7 +33195,7 @@
       </c>
       <c r="E1214" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33222,7 +33222,7 @@
       </c>
       <c r="E1215" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33249,7 +33249,7 @@
       </c>
       <c r="E1216" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33303,7 +33303,7 @@
       </c>
       <c r="E1218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33357,7 +33357,7 @@
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33384,7 +33384,7 @@
       </c>
       <c r="E1221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33438,7 +33438,7 @@
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="E1224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="E1225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33519,7 +33519,7 @@
       </c>
       <c r="E1226" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="E1227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33573,7 +33573,7 @@
       </c>
       <c r="E1228" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33600,7 +33600,7 @@
       </c>
       <c r="E1229" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33627,7 +33627,7 @@
       </c>
       <c r="E1230" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="E1231" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="E1232" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33708,7 +33708,7 @@
       </c>
       <c r="E1233" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33735,7 +33735,7 @@
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33762,7 +33762,7 @@
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33789,7 +33789,7 @@
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33816,7 +33816,7 @@
       </c>
       <c r="E1237" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="E1238" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33870,7 +33870,7 @@
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="E1240" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33924,7 +33924,7 @@
       </c>
       <c r="E1241" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33951,7 +33951,7 @@
       </c>
       <c r="E1242" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33978,7 +33978,7 @@
       </c>
       <c r="E1243" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34005,7 +34005,7 @@
       </c>
       <c r="E1244" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="E1245" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34059,7 +34059,7 @@
       </c>
       <c r="E1246" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34086,7 +34086,7 @@
       </c>
       <c r="E1247" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34113,7 +34113,7 @@
       </c>
       <c r="E1248" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34140,7 +34140,7 @@
       </c>
       <c r="E1249" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34167,7 +34167,7 @@
       </c>
       <c r="E1250" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="E1251" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34221,7 +34221,7 @@
       </c>
       <c r="E1252" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34248,7 +34248,7 @@
       </c>
       <c r="E1253" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34275,7 +34275,7 @@
       </c>
       <c r="E1254" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="E1255" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34329,7 +34329,7 @@
       </c>
       <c r="E1256" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34356,7 +34356,7 @@
       </c>
       <c r="E1257" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34383,7 +34383,7 @@
       </c>
       <c r="E1258" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="E1259" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34437,7 +34437,7 @@
       </c>
       <c r="E1260" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34464,7 +34464,7 @@
       </c>
       <c r="E1261" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="E1262" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34518,7 +34518,7 @@
       </c>
       <c r="E1263" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34545,7 +34545,7 @@
       </c>
       <c r="E1264" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34572,7 +34572,7 @@
       </c>
       <c r="E1265" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34599,7 +34599,7 @@
       </c>
       <c r="E1266" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
       </c>
       <c r="E1267" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
       </c>
       <c r="E1268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34680,7 +34680,7 @@
       </c>
       <c r="E1269" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34707,7 +34707,7 @@
       </c>
       <c r="E1270" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34734,7 +34734,7 @@
       </c>
       <c r="E1271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34761,7 +34761,7 @@
       </c>
       <c r="E1272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34788,7 +34788,7 @@
       </c>
       <c r="E1273" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="E1274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34842,7 +34842,7 @@
       </c>
       <c r="E1275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="E1276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34896,7 +34896,7 @@
       </c>
       <c r="E1277" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="E1278" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34950,7 +34950,7 @@
       </c>
       <c r="E1279" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34977,7 +34977,7 @@
       </c>
       <c r="E1280" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35004,7 +35004,7 @@
       </c>
       <c r="E1281" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="E1282" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35058,7 +35058,7 @@
       </c>
       <c r="E1283" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35085,7 +35085,7 @@
       </c>
       <c r="E1284" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35112,7 +35112,7 @@
       </c>
       <c r="E1285" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35139,7 +35139,7 @@
       </c>
       <c r="E1286" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35166,7 +35166,7 @@
       </c>
       <c r="E1287" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35193,7 +35193,7 @@
       </c>
       <c r="E1288" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35220,7 +35220,7 @@
       </c>
       <c r="E1289" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35247,7 +35247,7 @@
       </c>
       <c r="E1290" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35274,7 +35274,7 @@
       </c>
       <c r="E1291" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35301,7 +35301,7 @@
       </c>
       <c r="E1292" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35328,7 +35328,7 @@
       </c>
       <c r="E1293" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35355,7 +35355,7 @@
       </c>
       <c r="E1294" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35382,7 +35382,7 @@
       </c>
       <c r="E1295" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35409,7 +35409,7 @@
       </c>
       <c r="E1296" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="E1297" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="E1298" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="E1299" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="E1300" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35544,7 +35544,7 @@
       </c>
       <c r="E1301" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35571,7 +35571,7 @@
       </c>
       <c r="E1302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35598,7 +35598,7 @@
       </c>
       <c r="E1303" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="E1304" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35652,7 +35652,7 @@
       </c>
       <c r="E1305" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35679,7 +35679,7 @@
       </c>
       <c r="E1306" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35706,7 +35706,7 @@
       </c>
       <c r="E1307" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35733,7 +35733,7 @@
       </c>
       <c r="E1308" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="E1309" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="E1310" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35814,7 +35814,7 @@
       </c>
       <c r="E1311" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35841,7 +35841,7 @@
       </c>
       <c r="E1312" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36226,7 +36226,7 @@
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1327" t="inlineStr">
@@ -36246,14 +36246,14 @@
       </c>
       <c r="E1327" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="E1328" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -36334,7 +36334,7 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1331" t="inlineStr">
@@ -36354,14 +36354,14 @@
       </c>
       <c r="E1331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1332" t="inlineStr">
@@ -36381,14 +36381,14 @@
       </c>
       <c r="E1332" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
@@ -36408,14 +36408,14 @@
       </c>
       <c r="E1333" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1334" t="inlineStr">
@@ -36435,7 +36435,7 @@
       </c>
       <c r="E1334" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -36496,7 +36496,7 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
@@ -36516,14 +36516,14 @@
       </c>
       <c r="E1337" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
@@ -36543,7 +36543,7 @@
       </c>
       <c r="E1338" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -36604,7 +36604,7 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
@@ -36624,14 +36624,14 @@
       </c>
       <c r="E1341" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
@@ -36651,14 +36651,14 @@
       </c>
       <c r="E1342" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
@@ -36678,14 +36678,14 @@
       </c>
       <c r="E1343" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
@@ -36705,14 +36705,14 @@
       </c>
       <c r="E1344" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
@@ -36732,7 +36732,7 @@
       </c>
       <c r="E1345" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -36793,7 +36793,7 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
@@ -36813,14 +36813,14 @@
       </c>
       <c r="E1348" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
@@ -36840,14 +36840,14 @@
       </c>
       <c r="E1349" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
@@ -36867,14 +36867,14 @@
       </c>
       <c r="E1350" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
@@ -36894,14 +36894,14 @@
       </c>
       <c r="E1351" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
@@ -36921,7 +36921,7 @@
       </c>
       <c r="E1352" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -37866,7 +37866,7 @@
       </c>
       <c r="E1387" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37893,7 +37893,7 @@
       </c>
       <c r="E1388" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="E1389" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37947,7 +37947,7 @@
       </c>
       <c r="E1390" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38116,7 +38116,7 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
@@ -38136,7 +38136,7 @@
       </c>
       <c r="E1397" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -38163,14 +38163,14 @@
       </c>
       <c r="E1398" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
@@ -38190,14 +38190,14 @@
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
@@ -38217,14 +38217,14 @@
       </c>
       <c r="E1400" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
@@ -38244,7 +38244,7 @@
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38271,14 +38271,14 @@
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -38325,14 +38325,14 @@
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
@@ -38352,14 +38352,14 @@
       </c>
       <c r="E1405" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
@@ -38379,14 +38379,14 @@
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
@@ -38406,7 +38406,7 @@
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38433,14 +38433,14 @@
       </c>
       <c r="E1408" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
@@ -38460,7 +38460,7 @@
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -38487,14 +38487,14 @@
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
@@ -38514,14 +38514,14 @@
       </c>
       <c r="E1411" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
@@ -38541,14 +38541,14 @@
       </c>
       <c r="E1412" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
@@ -38568,7 +38568,7 @@
       </c>
       <c r="E1413" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38595,7 +38595,7 @@
       </c>
       <c r="E1414" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38649,7 +38649,7 @@
       </c>
       <c r="E1416" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38676,7 +38676,7 @@
       </c>
       <c r="E1417" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38730,7 +38730,7 @@
       </c>
       <c r="E1419" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38757,7 +38757,7 @@
       </c>
       <c r="E1420" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38926,7 +38926,7 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
@@ -38946,14 +38946,14 @@
       </c>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
@@ -38973,14 +38973,14 @@
       </c>
       <c r="E1428" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -39000,14 +39000,14 @@
       </c>
       <c r="E1429" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
@@ -39027,14 +39027,14 @@
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
@@ -39054,14 +39054,14 @@
       </c>
       <c r="E1431" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
@@ -39081,14 +39081,14 @@
       </c>
       <c r="E1432" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
@@ -39108,14 +39108,14 @@
       </c>
       <c r="E1433" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
@@ -39135,14 +39135,14 @@
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
@@ -39162,14 +39162,14 @@
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
@@ -39189,14 +39189,14 @@
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
@@ -39216,14 +39216,14 @@
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -39270,7 +39270,7 @@
       </c>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39297,7 +39297,7 @@
       </c>
       <c r="E1440" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39324,7 +39324,7 @@
       </c>
       <c r="E1441" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39351,7 +39351,7 @@
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39378,7 +39378,7 @@
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39405,7 +39405,7 @@
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39432,7 +39432,7 @@
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39459,7 +39459,7 @@
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39486,7 +39486,7 @@
       </c>
       <c r="E1447" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39513,7 +39513,7 @@
       </c>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39540,7 +39540,7 @@
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39567,7 +39567,7 @@
       </c>
       <c r="E1450" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -39736,7 +39736,7 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
@@ -39756,7 +39756,7 @@
       </c>
       <c r="E1457" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -39783,14 +39783,14 @@
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -39871,7 +39871,7 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
@@ -39891,14 +39891,14 @@
       </c>
       <c r="E1462" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
@@ -39918,7 +39918,7 @@
       </c>
       <c r="E1463" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -39945,14 +39945,14 @@
       </c>
       <c r="E1464" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
@@ -39972,7 +39972,7 @@
       </c>
       <c r="E1465" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -40033,7 +40033,7 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
@@ -40053,7 +40053,7 @@
       </c>
       <c r="E1468" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -40708,7 +40708,7 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
@@ -40728,14 +40728,14 @@
       </c>
       <c r="E1493" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role S in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
@@ -40755,14 +40755,14 @@
       </c>
       <c r="E1494" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role S in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role S in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
@@ -40782,7 +40782,7 @@
       </c>
       <c r="E1495" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -40809,14 +40809,14 @@
       </c>
       <c r="E1496" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role S in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
@@ -40836,14 +40836,14 @@
       </c>
       <c r="E1497" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
@@ -40863,14 +40863,14 @@
       </c>
       <c r="E1498" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
@@ -40890,14 +40890,14 @@
       </c>
       <c r="E1499" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role S in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
@@ -40917,14 +40917,14 @@
       </c>
       <c r="E1500" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role S in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role S in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="E1501" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -40971,14 +40971,14 @@
       </c>
       <c r="E1502" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role S in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
@@ -40998,14 +40998,14 @@
       </c>
       <c r="E1503" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
@@ -41025,14 +41025,14 @@
       </c>
       <c r="E1504" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
@@ -41052,7 +41052,7 @@
       </c>
       <c r="E1505" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41086,7 +41086,7 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
@@ -41106,14 +41106,14 @@
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -41133,14 +41133,14 @@
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
@@ -41160,14 +41160,14 @@
       </c>
       <c r="E1509" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
@@ -41187,7 +41187,7 @@
       </c>
       <c r="E1510" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41241,7 +41241,7 @@
       </c>
       <c r="E1512" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41275,7 +41275,7 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
@@ -41295,7 +41295,7 @@
       </c>
       <c r="E1514" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41376,7 +41376,7 @@
       </c>
       <c r="E1517" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41403,7 +41403,7 @@
       </c>
       <c r="E1518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41437,7 +41437,7 @@
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl.ClassC</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
@@ -41457,7 +41457,7 @@
       </c>
       <c r="E1520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41484,14 +41484,14 @@
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
@@ -41511,14 +41511,14 @@
       </c>
       <c r="E1522" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
@@ -41538,14 +41538,14 @@
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl.ClassA</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41592,14 +41592,14 @@
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3sg.ClassB</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
@@ -41619,7 +41619,7 @@
       </c>
       <c r="E1526" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41646,14 +41646,14 @@
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
@@ -41673,14 +41673,14 @@
       </c>
       <c r="E1528" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="E1529" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41727,14 +41727,14 @@
       </c>
       <c r="E1530" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
@@ -41754,14 +41754,14 @@
       </c>
       <c r="E1531" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
@@ -41781,14 +41781,14 @@
       </c>
       <c r="E1532" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3sg.ClassC</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
@@ -41808,7 +41808,7 @@
       </c>
       <c r="E1533" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41835,14 +41835,14 @@
       </c>
       <c r="E1534" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
@@ -41862,14 +41862,14 @@
       </c>
       <c r="E1535" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
@@ -41889,14 +41889,14 @@
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
@@ -41916,7 +41916,7 @@
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41943,14 +41943,14 @@
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
@@ -41970,7 +41970,7 @@
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41997,14 +41997,14 @@
       </c>
       <c r="E1540" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>3sg.ClassC</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
@@ -42024,7 +42024,7 @@
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42051,14 +42051,14 @@
       </c>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>3sg.ClassB</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42105,14 +42105,14 @@
       </c>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1545" t="inlineStr">
@@ -42132,14 +42132,14 @@
       </c>
       <c r="E1545" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1546" t="inlineStr">
@@ -42159,14 +42159,14 @@
       </c>
       <c r="E1546" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1547" t="inlineStr">
@@ -42186,14 +42186,14 @@
       </c>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1548" t="inlineStr">
@@ -42213,14 +42213,14 @@
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1549" t="inlineStr">
@@ -42240,14 +42240,14 @@
       </c>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1550" t="inlineStr">
@@ -42267,14 +42267,14 @@
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>3pl.ClassC</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1551" t="inlineStr">
@@ -42294,7 +42294,7 @@
       </c>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42321,14 +42321,14 @@
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1553" t="inlineStr">
@@ -42348,14 +42348,14 @@
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
@@ -42375,14 +42375,14 @@
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>3pl.ClassA</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
@@ -42402,7 +42402,7 @@
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42429,14 +42429,14 @@
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1557" t="inlineStr">
@@ -42456,14 +42456,14 @@
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1558" t="inlineStr">
@@ -42483,14 +42483,14 @@
       </c>
       <c r="E1558" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1559" t="inlineStr">
@@ -42510,14 +42510,14 @@
       </c>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1560" t="inlineStr">
@@ -42537,14 +42537,14 @@
       </c>
       <c r="E1560" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1561" t="inlineStr">
@@ -42564,14 +42564,14 @@
       </c>
       <c r="E1561" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1562" t="inlineStr">
@@ -42591,14 +42591,14 @@
       </c>
       <c r="E1562" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1563" t="inlineStr">
@@ -42618,14 +42618,14 @@
       </c>
       <c r="E1563" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1564" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="E1564" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -42706,7 +42706,7 @@
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1567" t="inlineStr">
@@ -42726,14 +42726,14 @@
       </c>
       <c r="E1567" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
@@ -42753,14 +42753,14 @@
       </c>
       <c r="E1568" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1569" t="inlineStr">
@@ -42780,14 +42780,14 @@
       </c>
       <c r="E1569" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1570" t="inlineStr">
@@ -42807,14 +42807,14 @@
       </c>
       <c r="E1570" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1571" t="inlineStr">
@@ -42834,14 +42834,14 @@
       </c>
       <c r="E1571" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1572" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -42888,7 +42888,7 @@
       </c>
       <c r="E1573" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42915,7 +42915,7 @@
       </c>
       <c r="E1574" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42996,7 +42996,7 @@
       </c>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43023,7 +43023,7 @@
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43104,7 +43104,7 @@
       </c>
       <c r="E1581" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43131,7 +43131,7 @@
       </c>
       <c r="E1582" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43165,7 +43165,7 @@
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1584" t="inlineStr">
@@ -43185,14 +43185,14 @@
       </c>
       <c r="E1584" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1585" t="inlineStr">
@@ -43212,14 +43212,14 @@
       </c>
       <c r="E1585" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1586" t="inlineStr">
@@ -43239,14 +43239,14 @@
       </c>
       <c r="E1586" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1587" t="inlineStr">
@@ -43266,14 +43266,14 @@
       </c>
       <c r="E1587" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1588" t="inlineStr">
@@ -43293,14 +43293,14 @@
       </c>
       <c r="E1588" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1589" t="inlineStr">
@@ -43320,14 +43320,14 @@
       </c>
       <c r="E1589" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1590" t="inlineStr">
@@ -43347,14 +43347,14 @@
       </c>
       <c r="E1590" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1591" t="inlineStr">
@@ -43374,7 +43374,7 @@
       </c>
       <c r="E1591" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43401,7 +43401,7 @@
       </c>
       <c r="E1592" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43428,14 +43428,14 @@
       </c>
       <c r="E1593" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1594" t="inlineStr">
@@ -43455,14 +43455,14 @@
       </c>
       <c r="E1594" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1595" t="inlineStr">
@@ -43482,7 +43482,7 @@
       </c>
       <c r="E1595" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -43509,7 +43509,7 @@
       </c>
       <c r="E1596" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43536,14 +43536,14 @@
       </c>
       <c r="E1597" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1598" t="inlineStr">
@@ -43563,14 +43563,14 @@
       </c>
       <c r="E1598" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1599" t="inlineStr">
@@ -43590,14 +43590,14 @@
       </c>
       <c r="E1599" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1600" t="inlineStr">
@@ -43617,14 +43617,14 @@
       </c>
       <c r="E1600" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1601" t="inlineStr">
@@ -43644,14 +43644,14 @@
       </c>
       <c r="E1601" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1602" t="inlineStr">
@@ -43671,14 +43671,14 @@
       </c>
       <c r="E1602" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1603" t="inlineStr">
@@ -43698,7 +43698,7 @@
       </c>
       <c r="E1603" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -43752,7 +43752,7 @@
       </c>
       <c r="E1605" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43779,7 +43779,7 @@
       </c>
       <c r="E1606" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43833,7 +43833,7 @@
       </c>
       <c r="E1608" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43887,7 +43887,7 @@
       </c>
       <c r="E1610" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43914,7 +43914,7 @@
       </c>
       <c r="E1611" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43968,7 +43968,7 @@
       </c>
       <c r="E1613" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43995,7 +43995,7 @@
       </c>
       <c r="E1614" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.FAM.M and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44049,7 +44049,7 @@
       </c>
       <c r="E1616" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44076,7 +44076,7 @@
       </c>
       <c r="E1617" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.FAM.F and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44103,7 +44103,7 @@
       </c>
       <c r="E1618" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.FAM.F and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44130,7 +44130,7 @@
       </c>
       <c r="E1619" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.FAM.M and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44157,7 +44157,7 @@
       </c>
       <c r="E1620" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44184,7 +44184,7 @@
       </c>
       <c r="E1621" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44211,7 +44211,7 @@
       </c>
       <c r="E1622" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.FAM.M and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44265,7 +44265,7 @@
       </c>
       <c r="E1624" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44292,7 +44292,7 @@
       </c>
       <c r="E1625" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.FAM.F and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44319,7 +44319,7 @@
       </c>
       <c r="E1626" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.FAM.F and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44346,7 +44346,7 @@
       </c>
       <c r="E1627" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.FAM.M and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44373,7 +44373,7 @@
       </c>
       <c r="E1628" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44400,7 +44400,7 @@
       </c>
       <c r="E1629" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44427,7 +44427,7 @@
       </c>
       <c r="E1630" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.FAM.M and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44481,7 +44481,7 @@
       </c>
       <c r="E1632" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44508,7 +44508,7 @@
       </c>
       <c r="E1633" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.FAM.F and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44535,7 +44535,7 @@
       </c>
       <c r="E1634" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.FAM.F and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44562,7 +44562,7 @@
       </c>
       <c r="E1635" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.FAM.M and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44589,7 +44589,7 @@
       </c>
       <c r="E1636" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44616,7 +44616,7 @@
       </c>
       <c r="E1637" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44643,7 +44643,7 @@
       </c>
       <c r="E1638" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.FAM.M and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44697,7 +44697,7 @@
       </c>
       <c r="E1640" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44724,7 +44724,7 @@
       </c>
       <c r="E1641" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.FAM.F and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44751,7 +44751,7 @@
       </c>
       <c r="E1642" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.FAM.F and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44778,7 +44778,7 @@
       </c>
       <c r="E1643" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.FAM.M and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44805,7 +44805,7 @@
       </c>
       <c r="E1644" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44832,7 +44832,7 @@
       </c>
       <c r="E1645" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>

--- a/outputs/alignment-warnings.xlsx
+++ b/outputs/alignment-warnings.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3927,14 +3927,14 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3954,14 +3954,14 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4008,14 +4008,14 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4069,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -4197,14 +4197,14 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4278,14 +4278,14 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4305,14 +4305,14 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4332,14 +4332,14 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4359,14 +4359,14 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4386,14 +4386,14 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4440,14 +4440,14 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4548,14 +4548,14 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -4629,14 +4629,14 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4737,14 +4737,14 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6168,14 +6168,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6195,14 +6195,14 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6222,14 +6222,14 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6249,14 +6249,14 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6357,14 +6357,14 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6384,14 +6384,14 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6438,14 +6438,14 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6465,14 +6465,14 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6492,14 +6492,14 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6519,14 +6519,14 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6546,14 +6546,14 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6573,14 +6573,14 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6708,14 +6708,14 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6735,14 +6735,14 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6816,14 +6816,14 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6843,14 +6843,14 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6870,14 +6870,14 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6897,14 +6897,14 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6978,14 +6978,14 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-generic and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-spec and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-generic and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-generic and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-generic and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-spec and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14376,7 +14376,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14457,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14673,7 +14673,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14754,7 +14754,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14781,7 +14781,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14808,7 +14808,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15078,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15240,7 +15240,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15348,7 +15348,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15672,7 +15672,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15942,7 +15942,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16779,7 +16779,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16860,7 +16860,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16914,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17049,14 +17049,14 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -17076,14 +17076,14 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -17103,14 +17103,14 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -17130,14 +17130,14 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>3pl.ClassA</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -17157,14 +17157,14 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl.ClassC</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -17184,14 +17184,14 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>3sg.ClassB</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -17211,14 +17211,14 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3sg.ClassB</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -17238,14 +17238,14 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -17265,14 +17265,14 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>3sg.ClassC</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -17292,14 +17292,14 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -17319,14 +17319,14 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17407,7 +17407,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>3sg.ClassC</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -17427,14 +17427,14 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -17454,14 +17454,14 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>3pl.ClassC</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -17481,14 +17481,14 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -17508,14 +17508,14 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -17535,14 +17535,14 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl.ClassA</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -17589,7 +17589,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17886,7 +17886,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17913,7 +17913,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -18750,14 +18750,14 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -18777,14 +18777,14 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -18804,14 +18804,14 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -18831,14 +18831,14 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -18858,14 +18858,14 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20181,7 +20181,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20424,7 +20424,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20586,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20721,7 +20721,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21342,7 +21342,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21396,7 +21396,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21423,7 +21423,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21558,7 +21558,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21639,7 +21639,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21990,7 +21990,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22368,7 +22368,7 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22422,7 +22422,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22476,7 +22476,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22530,7 +22530,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22611,7 +22611,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22665,7 +22665,7 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22719,7 +22719,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22746,7 +22746,7 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22773,7 +22773,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22827,7 +22827,7 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22881,7 +22881,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22935,7 +22935,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22962,7 +22962,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23016,7 +23016,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23043,7 +23043,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23124,7 +23124,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23151,7 +23151,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23232,7 +23232,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23313,7 +23313,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23394,7 +23394,7 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23448,7 +23448,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23475,7 +23475,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23502,7 +23502,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23529,7 +23529,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23610,7 +23610,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23637,7 +23637,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23691,7 +23691,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23718,14 +23718,14 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -23745,14 +23745,14 @@
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -23772,14 +23772,14 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23880,7 +23880,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23907,7 +23907,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23934,7 +23934,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23961,14 +23961,14 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -23988,7 +23988,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24015,7 +24015,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24042,14 +24042,14 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -24069,7 +24069,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24123,7 +24123,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24150,7 +24150,7 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24204,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24231,14 +24231,14 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24285,7 +24285,7 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24366,7 +24366,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24420,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24501,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24852,7 +24852,7 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25095,14 +25095,14 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -25122,14 +25122,14 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -25149,14 +25149,14 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25203,14 +25203,14 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -25230,14 +25230,14 @@
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25284,14 +25284,14 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -25311,14 +25311,14 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -25338,7 +25338,7 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25365,14 +25365,14 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -25392,14 +25392,14 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25446,14 +25446,14 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -25473,14 +25473,14 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -25500,14 +25500,14 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25554,14 +25554,14 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -25581,14 +25581,14 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -25608,7 +25608,7 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25635,14 +25635,14 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -25662,14 +25662,14 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -25689,7 +25689,7 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25716,14 +25716,14 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
@@ -25743,14 +25743,14 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26148,7 +26148,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26256,7 +26256,7 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26634,14 +26634,14 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
@@ -26661,14 +26661,14 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -26688,14 +26688,14 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
@@ -26715,14 +26715,14 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -26742,14 +26742,14 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
@@ -26769,14 +26769,14 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
@@ -26796,14 +26796,14 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
@@ -26823,14 +26823,14 @@
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -26850,14 +26850,14 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
@@ -26877,14 +26877,14 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
@@ -26904,7 +26904,7 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26958,14 +26958,14 @@
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
@@ -26985,14 +26985,14 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -27012,7 +27012,7 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27066,14 +27066,14 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
@@ -27093,14 +27093,14 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -27120,14 +27120,14 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
@@ -27147,14 +27147,14 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -27174,14 +27174,14 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
@@ -27201,14 +27201,14 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -27228,14 +27228,14 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
@@ -27255,14 +27255,14 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
@@ -27282,14 +27282,14 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
@@ -27309,14 +27309,14 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27390,14 +27390,14 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
@@ -27417,14 +27417,14 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
@@ -27444,7 +27444,7 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27498,7 +27498,7 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27552,7 +27552,7 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27606,7 +27606,7 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27633,7 +27633,7 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27660,7 +27660,7 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27714,7 +27714,7 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27768,7 +27768,7 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27822,7 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27930,7 +27930,7 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28038,7 +28038,7 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28065,7 +28065,7 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28092,7 +28092,7 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28146,7 +28146,7 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28200,7 +28200,7 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28308,7 +28308,7 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28362,7 +28362,7 @@
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28389,7 +28389,7 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29037,7 +29037,7 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29118,7 +29118,7 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29145,7 +29145,7 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29172,7 @@
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29253,7 +29253,7 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29334,7 +29334,7 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29685,7 +29685,7 @@
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29766,7 +29766,7 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29793,7 +29793,7 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29820,7 +29820,7 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29874,7 +29874,7 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29928,7 +29928,7 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29982,7 +29982,7 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30009,7 +30009,7 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30036,7 +30036,7 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30090,7 +30090,7 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30117,7 +30117,7 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30144,7 +30144,7 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30225,7 +30225,7 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30333,7 +30333,7 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30360,7 +30360,7 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30441,7 +30441,7 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30630,7 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30657,7 +30657,7 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30792,7 +30792,7 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30873,7 +30873,7 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30900,7 +30900,7 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30981,7 +30981,7 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31062,7 +31062,7 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31089,7 +31089,7 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31116,7 +31116,7 @@
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31170,7 +31170,7 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31224,7 +31224,7 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31278,7 +31278,7 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31305,7 +31305,7 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31332,7 +31332,7 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31440,7 +31440,7 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31494,7 +31494,7 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31521,7 +31521,7 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31548,7 +31548,7 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31602,7 +31602,7 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32061,7 +32061,7 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32088,7 +32088,7 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32142,7 +32142,7 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32169,7 +32169,7 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32196,7 +32196,7 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32304,7 +32304,7 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32358,7 +32358,7 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32412,7 +32412,7 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32466,7 +32466,7 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32520,7 +32520,7 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32574,7 +32574,7 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32601,7 +32601,7 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32628,7 +32628,7 @@
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33303,7 +33303,7 @@
       </c>
       <c r="E1218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33357,7 +33357,7 @@
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33384,7 +33384,7 @@
       </c>
       <c r="E1221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33438,7 +33438,7 @@
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="E1224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="E1225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33519,7 +33519,7 @@
       </c>
       <c r="E1226" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="E1227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33573,7 +33573,7 @@
       </c>
       <c r="E1228" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33600,7 +33600,7 @@
       </c>
       <c r="E1229" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33627,7 +33627,7 @@
       </c>
       <c r="E1230" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="E1231" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="E1232" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33708,7 +33708,7 @@
       </c>
       <c r="E1233" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33735,7 +33735,7 @@
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34383,7 +34383,7 @@
       </c>
       <c r="E1258" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="E1259" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34437,7 +34437,7 @@
       </c>
       <c r="E1260" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34464,7 +34464,7 @@
       </c>
       <c r="E1261" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="E1262" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34518,7 +34518,7 @@
       </c>
       <c r="E1263" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34545,7 +34545,7 @@
       </c>
       <c r="E1264" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34599,7 +34599,7 @@
       </c>
       <c r="E1266" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
       </c>
       <c r="E1267" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
       </c>
       <c r="E1268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34680,7 +34680,7 @@
       </c>
       <c r="E1269" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34707,7 +34707,7 @@
       </c>
       <c r="E1270" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34734,7 +34734,7 @@
       </c>
       <c r="E1271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34761,7 +34761,7 @@
       </c>
       <c r="E1272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34788,7 +34788,7 @@
       </c>
       <c r="E1273" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="E1274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34842,7 +34842,7 @@
       </c>
       <c r="E1275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="E1276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34896,7 +34896,7 @@
       </c>
       <c r="E1277" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="E1278" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34950,7 +34950,7 @@
       </c>
       <c r="E1279" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35409,7 +35409,7 @@
       </c>
       <c r="E1296" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="E1297" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="E1298" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="E1299" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="E1300" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35544,7 +35544,7 @@
       </c>
       <c r="E1301" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35571,7 +35571,7 @@
       </c>
       <c r="E1302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35598,7 +35598,7 @@
       </c>
       <c r="E1303" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="E1304" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35652,7 +35652,7 @@
       </c>
       <c r="E1305" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35679,7 +35679,7 @@
       </c>
       <c r="E1306" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35706,7 +35706,7 @@
       </c>
       <c r="E1307" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35733,7 +35733,7 @@
       </c>
       <c r="E1308" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="E1309" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="E1310" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35814,7 +35814,7 @@
       </c>
       <c r="E1311" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="E1314" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35922,7 +35922,7 @@
       </c>
       <c r="E1315" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35949,7 +35949,7 @@
       </c>
       <c r="E1316" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35976,7 +35976,7 @@
       </c>
       <c r="E1317" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36003,7 +36003,7 @@
       </c>
       <c r="E1318" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="E1319" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36057,7 +36057,7 @@
       </c>
       <c r="E1320" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36084,7 +36084,7 @@
       </c>
       <c r="E1321" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36111,7 +36111,7 @@
       </c>
       <c r="E1322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36138,7 +36138,7 @@
       </c>
       <c r="E1323" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="E1324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="E1325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36219,7 +36219,7 @@
       </c>
       <c r="E1326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36246,7 +36246,7 @@
       </c>
       <c r="E1327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36273,7 +36273,7 @@
       </c>
       <c r="E1328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36300,7 +36300,7 @@
       </c>
       <c r="E1329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36327,7 +36327,7 @@
       </c>
       <c r="E1330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36354,7 +36354,7 @@
       </c>
       <c r="E1331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36381,7 +36381,7 @@
       </c>
       <c r="E1332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36408,7 +36408,7 @@
       </c>
       <c r="E1333" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36435,7 +36435,7 @@
       </c>
       <c r="E1334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="E1335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36489,7 +36489,7 @@
       </c>
       <c r="E1336" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36516,7 +36516,7 @@
       </c>
       <c r="E1337" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="E1338" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="E1339" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36597,7 +36597,7 @@
       </c>
       <c r="E1340" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36624,7 +36624,7 @@
       </c>
       <c r="E1341" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36651,7 +36651,7 @@
       </c>
       <c r="E1342" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="E1343" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36705,7 +36705,7 @@
       </c>
       <c r="E1344" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36732,7 +36732,7 @@
       </c>
       <c r="E1345" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36759,7 +36759,7 @@
       </c>
       <c r="E1346" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="E1347" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36813,7 +36813,7 @@
       </c>
       <c r="E1348" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36840,7 +36840,7 @@
       </c>
       <c r="E1349" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36894,7 +36894,7 @@
       </c>
       <c r="E1351" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
       </c>
       <c r="E1352" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="E1353" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36975,7 +36975,7 @@
       </c>
       <c r="E1354" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="E1355" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37029,7 +37029,7 @@
       </c>
       <c r="E1356" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37056,7 +37056,7 @@
       </c>
       <c r="E1357" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37083,7 +37083,7 @@
       </c>
       <c r="E1358" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37110,7 +37110,7 @@
       </c>
       <c r="E1359" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37137,7 +37137,7 @@
       </c>
       <c r="E1360" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37218,7 +37218,7 @@
       </c>
       <c r="E1363" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37245,7 +37245,7 @@
       </c>
       <c r="E1364" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37272,7 +37272,7 @@
       </c>
       <c r="E1365" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37299,7 +37299,7 @@
       </c>
       <c r="E1366" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37326,7 +37326,7 @@
       </c>
       <c r="E1367" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37353,7 +37353,7 @@
       </c>
       <c r="E1368" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37380,7 +37380,7 @@
       </c>
       <c r="E1369" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="E1370" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37434,7 +37434,7 @@
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37461,7 +37461,7 @@
       </c>
       <c r="E1372" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37488,7 +37488,7 @@
       </c>
       <c r="E1373" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37515,7 +37515,7 @@
       </c>
       <c r="E1374" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37542,7 +37542,7 @@
       </c>
       <c r="E1375" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="E1376" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37623,7 +37623,7 @@
       </c>
       <c r="E1378" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37650,7 +37650,7 @@
       </c>
       <c r="E1379" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37677,7 +37677,7 @@
       </c>
       <c r="E1380" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37704,7 +37704,7 @@
       </c>
       <c r="E1381" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37731,7 +37731,7 @@
       </c>
       <c r="E1382" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="E1383" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37785,7 +37785,7 @@
       </c>
       <c r="E1384" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37812,7 +37812,7 @@
       </c>
       <c r="E1385" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37839,7 +37839,7 @@
       </c>
       <c r="E1386" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37866,7 +37866,7 @@
       </c>
       <c r="E1387" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37947,7 +37947,7 @@
       </c>
       <c r="E1390" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37974,7 +37974,7 @@
       </c>
       <c r="E1391" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="E1392" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38028,7 +38028,7 @@
       </c>
       <c r="E1393" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38055,7 +38055,7 @@
       </c>
       <c r="E1394" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38082,7 +38082,7 @@
       </c>
       <c r="E1395" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38109,7 +38109,7 @@
       </c>
       <c r="E1396" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38136,7 +38136,7 @@
       </c>
       <c r="E1397" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38163,7 +38163,7 @@
       </c>
       <c r="E1398" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38217,7 +38217,7 @@
       </c>
       <c r="E1400" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38244,7 +38244,7 @@
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38352,7 +38352,7 @@
       </c>
       <c r="E1405" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38379,7 +38379,7 @@
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38406,7 +38406,7 @@
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38460,7 +38460,7 @@
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38487,7 +38487,7 @@
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38514,7 +38514,7 @@
       </c>
       <c r="E1411" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38541,7 +38541,7 @@
       </c>
       <c r="E1412" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38568,7 +38568,7 @@
       </c>
       <c r="E1413" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38622,7 +38622,7 @@
       </c>
       <c r="E1415" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38649,7 +38649,7 @@
       </c>
       <c r="E1416" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38676,7 +38676,7 @@
       </c>
       <c r="E1417" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38703,7 +38703,7 @@
       </c>
       <c r="E1418" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38730,7 +38730,7 @@
       </c>
       <c r="E1419" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39115,7 +39115,7 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
@@ -39135,14 +39135,14 @@
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
@@ -39162,14 +39162,14 @@
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
@@ -39189,14 +39189,14 @@
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
@@ -39216,14 +39216,14 @@
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
@@ -39243,14 +39243,14 @@
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
@@ -39270,14 +39270,14 @@
       </c>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
@@ -39297,14 +39297,14 @@
       </c>
       <c r="E1440" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
@@ -39324,14 +39324,14 @@
       </c>
       <c r="E1441" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
@@ -39351,14 +39351,14 @@
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
@@ -39378,14 +39378,14 @@
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
@@ -39405,14 +39405,14 @@
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
@@ -39432,14 +39432,14 @@
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
@@ -39459,14 +39459,14 @@
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
@@ -39486,7 +39486,7 @@
       </c>
       <c r="E1447" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -39520,7 +39520,7 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
@@ -39540,14 +39540,14 @@
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
@@ -39567,14 +39567,14 @@
       </c>
       <c r="E1450" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
@@ -39594,14 +39594,14 @@
       </c>
       <c r="E1451" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
@@ -39621,14 +39621,14 @@
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
@@ -39648,14 +39648,14 @@
       </c>
       <c r="E1453" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
@@ -39675,7 +39675,7 @@
       </c>
       <c r="E1454" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -39709,7 +39709,7 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
@@ -39729,14 +39729,14 @@
       </c>
       <c r="E1456" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
@@ -39756,14 +39756,14 @@
       </c>
       <c r="E1457" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
@@ -39783,14 +39783,14 @@
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41106,14 +41106,14 @@
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41160,7 +41160,7 @@
       </c>
       <c r="E1509" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41187,14 +41187,14 @@
       </c>
       <c r="E1510" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
@@ -41214,7 +41214,7 @@
       </c>
       <c r="E1511" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41268,14 +41268,14 @@
       </c>
       <c r="E1513" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
@@ -41295,7 +41295,7 @@
       </c>
       <c r="E1514" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41322,7 +41322,7 @@
       </c>
       <c r="E1515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41349,14 +41349,14 @@
       </c>
       <c r="E1516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
@@ -41376,7 +41376,7 @@
       </c>
       <c r="E1517" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41430,14 +41430,14 @@
       </c>
       <c r="E1519" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
@@ -41457,7 +41457,7 @@
       </c>
       <c r="E1520" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41484,7 +41484,7 @@
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41511,14 +41511,14 @@
       </c>
       <c r="E1522" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
@@ -41538,7 +41538,7 @@
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41565,7 +41565,7 @@
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41592,7 +41592,7 @@
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41619,7 +41619,7 @@
       </c>
       <c r="E1526" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41646,7 +41646,7 @@
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41673,7 +41673,7 @@
       </c>
       <c r="E1528" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41700,7 +41700,7 @@
       </c>
       <c r="E1529" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41869,7 +41869,7 @@
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
@@ -41889,14 +41889,14 @@
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
@@ -41916,14 +41916,14 @@
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
@@ -41943,14 +41943,14 @@
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
@@ -41970,7 +41970,7 @@
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41997,14 +41997,14 @@
       </c>
       <c r="E1540" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
@@ -42024,14 +42024,14 @@
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
@@ -42051,14 +42051,14 @@
       </c>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
@@ -42078,14 +42078,14 @@
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1544" t="inlineStr">
@@ -42105,14 +42105,14 @@
       </c>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1545" t="inlineStr">
@@ -42132,7 +42132,7 @@
       </c>
       <c r="E1545" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -42159,14 +42159,14 @@
       </c>
       <c r="E1546" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1547" t="inlineStr">
@@ -42186,7 +42186,7 @@
       </c>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -42213,7 +42213,7 @@
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42240,7 +42240,7 @@
       </c>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42267,7 +42267,7 @@
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42294,7 +42294,7 @@
       </c>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42321,7 +42321,7 @@
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42348,7 +42348,7 @@
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42375,7 +42375,7 @@
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42402,7 +42402,7 @@
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42429,7 +42429,7 @@
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42456,7 +42456,7 @@
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42483,7 +42483,7 @@
       </c>
       <c r="E1558" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42510,7 +42510,7 @@
       </c>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42733,7 +42733,7 @@
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
@@ -42753,14 +42753,14 @@
       </c>
       <c r="E1568" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1569" t="inlineStr">
@@ -42780,7 +42780,7 @@
       </c>
       <c r="E1569" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -42841,7 +42841,7 @@
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1572" t="inlineStr">
@@ -42861,14 +42861,14 @@
       </c>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1573" t="inlineStr">
@@ -42888,14 +42888,14 @@
       </c>
       <c r="E1573" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1574" t="inlineStr">
@@ -42915,14 +42915,14 @@
       </c>
       <c r="E1574" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1575" t="inlineStr">
@@ -42942,7 +42942,7 @@
       </c>
       <c r="E1575" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -43003,7 +43003,7 @@
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1578" t="inlineStr">
@@ -43023,14 +43023,14 @@
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1579" t="inlineStr">
@@ -43050,7 +43050,7 @@
       </c>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>

--- a/outputs/alignment-warnings.xlsx
+++ b/outputs/alignment-warnings.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4035,14 +4035,14 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4062,14 +4062,14 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4170,14 +4170,14 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -4224,14 +4224,14 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4251,14 +4251,14 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4278,14 +4278,14 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4305,14 +4305,14 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4467,14 +4467,14 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4548,14 +4548,14 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4602,14 +4602,14 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -4656,14 +4656,14 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4683,14 +4683,14 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4737,14 +4737,14 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6168,14 +6168,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6195,14 +6195,14 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6222,14 +6222,14 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6249,14 +6249,14 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6276,14 +6276,14 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6303,14 +6303,14 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6330,14 +6330,14 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6357,14 +6357,14 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6384,14 +6384,14 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6438,14 +6438,14 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6465,14 +6465,14 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6492,14 +6492,14 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6519,14 +6519,14 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6546,14 +6546,14 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6573,14 +6573,14 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6600,14 +6600,14 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6627,14 +6627,14 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6654,14 +6654,14 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6708,14 +6708,14 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6735,14 +6735,14 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6816,14 +6816,14 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6897,14 +6897,14 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6985,7 +6985,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-spec and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-generic and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-generic and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-generic and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-spec and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-spec and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-spec and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-generic and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12682,7 +12682,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role S in language: kala1400, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12729,14 +12729,14 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role S in language: kala1400, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14457,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14673,7 +14673,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14754,7 +14754,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14808,7 +14808,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15240,7 +15240,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15348,7 +15348,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15672,7 +15672,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15942,7 +15942,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15996,7 +15996,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16779,7 +16779,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16806,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16860,7 +16860,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16914,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17049,14 +17049,14 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3sg.ClassB</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -17076,14 +17076,14 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -17103,14 +17103,14 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>3sg.ClassC</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -17130,14 +17130,14 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -17157,14 +17157,14 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>3pl.ClassC</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -17184,14 +17184,14 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -17211,14 +17211,14 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>3sg.ClassB</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -17238,14 +17238,14 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -17265,14 +17265,14 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>3sg.ClassC</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -17292,14 +17292,14 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -17319,14 +17319,14 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -17346,14 +17346,14 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>3pl.ClassC</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -17373,14 +17373,14 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -17400,14 +17400,14 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -17427,14 +17427,14 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -17481,14 +17481,14 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>3pl.ClassA</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -17508,14 +17508,14 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -17535,14 +17535,14 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>3pl.ClassA</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -17562,14 +17562,14 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -18750,14 +18750,14 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -18777,14 +18777,14 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -18804,14 +18804,14 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -18831,14 +18831,14 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -18858,14 +18858,14 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19162,7 +19162,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -19182,14 +19182,14 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -19209,14 +19209,14 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -19236,14 +19236,14 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -19263,14 +19263,14 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -19290,14 +19290,14 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -19317,14 +19317,14 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -19344,14 +19344,14 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19540,7 +19540,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -19560,14 +19560,14 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -19587,14 +19587,14 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -19614,14 +19614,14 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -19641,14 +19641,14 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19702,7 +19702,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -19722,14 +19722,14 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -19749,14 +19749,14 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19911,7 +19911,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20181,7 +20181,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20424,7 +20424,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20586,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20721,7 +20721,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21342,7 +21342,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21396,7 +21396,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21423,7 +21423,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21558,7 +21558,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21639,7 +21639,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21666,14 +21666,14 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -21727,7 +21727,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -21747,14 +21747,14 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -21808,7 +21808,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22422,7 +22422,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22476,7 +22476,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22530,7 +22530,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22611,7 +22611,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22665,7 +22665,7 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22719,7 +22719,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22746,7 +22746,7 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22773,7 +22773,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22827,7 +22827,7 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22935,7 +22935,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22962,7 +22962,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23016,7 +23016,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23043,7 +23043,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23124,7 +23124,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23151,7 +23151,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23232,7 +23232,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23313,7 +23313,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23394,7 +23394,7 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23448,7 +23448,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23610,7 +23610,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23637,7 +23637,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23725,7 +23725,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -23745,14 +23745,14 @@
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -23772,14 +23772,14 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23880,7 +23880,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23907,7 +23907,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23934,7 +23934,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23988,7 +23988,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24015,14 +24015,14 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -24042,14 +24042,14 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -24069,7 +24069,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24123,7 +24123,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24150,7 +24150,7 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24204,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24231,14 +24231,14 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24285,7 +24285,7 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24312,7 +24312,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24366,7 +24366,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24420,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24447,7 +24447,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24501,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24825,7 +24825,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24906,7 +24906,7 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25122,14 +25122,14 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -25149,14 +25149,14 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25230,14 +25230,14 @@
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -25257,14 +25257,14 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -25284,14 +25284,14 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -25311,7 +25311,7 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25338,14 +25338,14 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -25365,7 +25365,7 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25392,14 +25392,14 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25473,14 +25473,14 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -25500,14 +25500,14 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25554,7 +25554,7 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25581,14 +25581,14 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -25608,14 +25608,14 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -25635,14 +25635,14 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -25662,7 +25662,7 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25689,14 +25689,14 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -25716,7 +25716,7 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25743,14 +25743,14 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -26479,7 +26479,7 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
@@ -26499,14 +26499,14 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: nort2980, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
@@ -26526,14 +26526,14 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: nort2980, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
@@ -26553,14 +26553,14 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: nort2980, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -26580,14 +26580,14 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: nort2980, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
@@ -26607,14 +26607,14 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -26634,14 +26634,14 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
@@ -26661,14 +26661,14 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -26688,14 +26688,14 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
@@ -26715,14 +26715,14 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -26742,14 +26742,14 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
@@ -26769,14 +26769,14 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
@@ -26796,14 +26796,14 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
@@ -26823,14 +26823,14 @@
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -26850,7 +26850,7 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -26904,7 +26904,7 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26985,7 +26985,7 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27012,7 +27012,7 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27066,14 +27066,14 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
@@ -27093,14 +27093,14 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -27120,14 +27120,14 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
@@ -27147,14 +27147,14 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -27174,14 +27174,14 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
@@ -27201,14 +27201,14 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -27228,14 +27228,14 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
@@ -27255,14 +27255,14 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
@@ -27282,7 +27282,7 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27309,14 +27309,14 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -27336,14 +27336,14 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
@@ -27363,7 +27363,7 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -27390,7 +27390,7 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27417,14 +27417,14 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
@@ -27444,14 +27444,14 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
@@ -27471,14 +27471,14 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -27498,14 +27498,14 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
@@ -27525,14 +27525,14 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
@@ -27552,14 +27552,14 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -27579,7 +27579,7 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -27606,7 +27606,7 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27633,7 +27633,7 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27660,7 +27660,7 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27714,7 +27714,7 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27930,7 +27930,7 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27957,7 +27957,7 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28038,7 +28038,7 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28065,7 +28065,7 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28092,7 +28092,7 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28146,7 +28146,7 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28173,7 +28173,7 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28200,7 +28200,7 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28308,7 +28308,7 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29037,7 +29037,7 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29118,7 +29118,7 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29253,7 +29253,7 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29685,7 +29685,7 @@
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29766,7 +29766,7 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29793,7 +29793,7 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29820,7 +29820,7 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29874,7 +29874,7 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29928,7 +29928,7 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29982,7 +29982,7 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30009,7 +30009,7 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30036,7 +30036,7 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30090,7 +30090,7 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30117,7 +30117,7 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30144,7 +30144,7 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30225,7 +30225,7 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30333,7 +30333,7 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30360,7 +30360,7 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30441,7 +30441,7 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30522,7 +30522,7 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30576,7 +30576,7 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30630,7 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30657,7 +30657,7 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30792,7 +30792,7 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30873,7 +30873,7 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30900,7 +30900,7 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30981,7 +30981,7 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31062,7 +31062,7 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31089,7 +31089,7 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31116,7 +31116,7 @@
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31170,7 +31170,7 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31224,7 +31224,7 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31278,7 +31278,7 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31305,7 +31305,7 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31332,7 +31332,7 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31440,7 +31440,7 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31521,7 +31521,7 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31548,7 +31548,7 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31602,7 +31602,7 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32061,7 +32061,7 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32088,7 +32088,7 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32142,7 +32142,7 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32169,7 +32169,7 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32196,7 +32196,7 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32250,7 +32250,7 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32304,7 +32304,7 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32358,7 +32358,7 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32412,7 +32412,7 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32466,7 +32466,7 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32520,7 +32520,7 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32574,7 +32574,7 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32628,7 +32628,7 @@
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33303,7 +33303,7 @@
       </c>
       <c r="E1218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33384,7 +33384,7 @@
       </c>
       <c r="E1221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33438,7 +33438,7 @@
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="E1224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="E1225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33519,7 +33519,7 @@
       </c>
       <c r="E1226" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="E1227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33573,7 +33573,7 @@
       </c>
       <c r="E1228" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33600,7 +33600,7 @@
       </c>
       <c r="E1229" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33627,7 +33627,7 @@
       </c>
       <c r="E1230" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="E1231" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="E1232" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33708,7 +33708,7 @@
       </c>
       <c r="E1233" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33735,14 +33735,14 @@
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">
@@ -33762,14 +33762,14 @@
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1236" t="inlineStr">
@@ -33789,7 +33789,7 @@
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -33816,14 +33816,14 @@
       </c>
       <c r="E1237" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1238" t="inlineStr">
@@ -33843,14 +33843,14 @@
       </c>
       <c r="E1238" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1239" t="inlineStr">
@@ -33870,14 +33870,14 @@
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1240" t="inlineStr">
@@ -33897,7 +33897,7 @@
       </c>
       <c r="E1240" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -33924,14 +33924,14 @@
       </c>
       <c r="E1241" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1242" t="inlineStr">
@@ -33951,7 +33951,7 @@
       </c>
       <c r="E1242" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -34086,7 +34086,7 @@
       </c>
       <c r="E1247" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34113,7 +34113,7 @@
       </c>
       <c r="E1248" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34140,7 +34140,7 @@
       </c>
       <c r="E1249" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34167,7 +34167,7 @@
       </c>
       <c r="E1250" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="E1251" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34221,7 +34221,7 @@
       </c>
       <c r="E1252" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34248,7 +34248,7 @@
       </c>
       <c r="E1253" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34275,7 +34275,7 @@
       </c>
       <c r="E1254" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34383,7 +34383,7 @@
       </c>
       <c r="E1258" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="E1259" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34437,7 +34437,7 @@
       </c>
       <c r="E1260" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34464,7 +34464,7 @@
       </c>
       <c r="E1261" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="E1262" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34518,7 +34518,7 @@
       </c>
       <c r="E1263" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34545,7 +34545,7 @@
       </c>
       <c r="E1264" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34572,7 +34572,7 @@
       </c>
       <c r="E1265" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34599,7 +34599,7 @@
       </c>
       <c r="E1266" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
       </c>
       <c r="E1267" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
       </c>
       <c r="E1268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34680,7 +34680,7 @@
       </c>
       <c r="E1269" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34707,7 +34707,7 @@
       </c>
       <c r="E1270" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34734,7 +34734,7 @@
       </c>
       <c r="E1271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34761,7 +34761,7 @@
       </c>
       <c r="E1272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34788,7 +34788,7 @@
       </c>
       <c r="E1273" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="E1274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34842,7 +34842,7 @@
       </c>
       <c r="E1275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="E1276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34896,7 +34896,7 @@
       </c>
       <c r="E1277" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="E1278" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34950,7 +34950,7 @@
       </c>
       <c r="E1279" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35355,7 +35355,7 @@
       </c>
       <c r="E1294" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35382,7 +35382,7 @@
       </c>
       <c r="E1295" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35409,7 +35409,7 @@
       </c>
       <c r="E1296" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="E1297" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="E1299" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="E1300" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35544,7 +35544,7 @@
       </c>
       <c r="E1301" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35571,7 +35571,7 @@
       </c>
       <c r="E1302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35598,7 +35598,7 @@
       </c>
       <c r="E1303" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="E1304" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35652,7 +35652,7 @@
       </c>
       <c r="E1305" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35679,7 +35679,7 @@
       </c>
       <c r="E1306" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35706,7 +35706,7 @@
       </c>
       <c r="E1307" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35733,7 +35733,7 @@
       </c>
       <c r="E1308" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="E1309" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="E1310" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35814,7 +35814,7 @@
       </c>
       <c r="E1311" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35841,7 +35841,7 @@
       </c>
       <c r="E1312" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="E1313" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="E1314" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35922,7 +35922,7 @@
       </c>
       <c r="E1315" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35976,7 +35976,7 @@
       </c>
       <c r="E1317" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36003,7 +36003,7 @@
       </c>
       <c r="E1318" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="E1319" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36057,7 +36057,7 @@
       </c>
       <c r="E1320" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36084,7 +36084,7 @@
       </c>
       <c r="E1321" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36111,7 +36111,7 @@
       </c>
       <c r="E1322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36138,7 +36138,7 @@
       </c>
       <c r="E1323" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="E1324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="E1325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36219,7 +36219,7 @@
       </c>
       <c r="E1326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36246,7 +36246,7 @@
       </c>
       <c r="E1327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36273,7 +36273,7 @@
       </c>
       <c r="E1328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36300,7 +36300,7 @@
       </c>
       <c r="E1329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36327,7 +36327,7 @@
       </c>
       <c r="E1330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36354,7 +36354,7 @@
       </c>
       <c r="E1331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36381,7 +36381,7 @@
       </c>
       <c r="E1332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36435,7 +36435,7 @@
       </c>
       <c r="E1334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="E1335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36489,7 +36489,7 @@
       </c>
       <c r="E1336" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36516,7 +36516,7 @@
       </c>
       <c r="E1337" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="E1338" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36597,7 +36597,7 @@
       </c>
       <c r="E1340" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36624,7 +36624,7 @@
       </c>
       <c r="E1341" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36651,7 +36651,7 @@
       </c>
       <c r="E1342" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="E1343" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36705,7 +36705,7 @@
       </c>
       <c r="E1344" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36759,7 +36759,7 @@
       </c>
       <c r="E1346" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="E1347" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36813,7 +36813,7 @@
       </c>
       <c r="E1348" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36840,7 +36840,7 @@
       </c>
       <c r="E1349" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36867,7 +36867,7 @@
       </c>
       <c r="E1350" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36894,7 +36894,7 @@
       </c>
       <c r="E1351" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="E1353" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36975,7 +36975,7 @@
       </c>
       <c r="E1354" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="E1355" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37029,7 +37029,7 @@
       </c>
       <c r="E1356" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37056,7 +37056,7 @@
       </c>
       <c r="E1357" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37083,7 +37083,7 @@
       </c>
       <c r="E1358" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37110,7 +37110,7 @@
       </c>
       <c r="E1359" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37137,7 +37137,7 @@
       </c>
       <c r="E1360" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37164,7 +37164,7 @@
       </c>
       <c r="E1361" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37191,7 +37191,7 @@
       </c>
       <c r="E1362" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37218,7 +37218,7 @@
       </c>
       <c r="E1363" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37245,7 +37245,7 @@
       </c>
       <c r="E1364" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37326,7 +37326,7 @@
       </c>
       <c r="E1367" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37353,7 +37353,7 @@
       </c>
       <c r="E1368" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37380,7 +37380,7 @@
       </c>
       <c r="E1369" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="E1370" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37434,7 +37434,7 @@
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37461,7 +37461,7 @@
       </c>
       <c r="E1372" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37488,7 +37488,7 @@
       </c>
       <c r="E1373" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37515,7 +37515,7 @@
       </c>
       <c r="E1374" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37542,7 +37542,7 @@
       </c>
       <c r="E1375" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="E1376" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37596,7 +37596,7 @@
       </c>
       <c r="E1377" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37623,7 +37623,7 @@
       </c>
       <c r="E1378" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37677,7 +37677,7 @@
       </c>
       <c r="E1380" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37704,7 +37704,7 @@
       </c>
       <c r="E1381" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37731,7 +37731,7 @@
       </c>
       <c r="E1382" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="E1383" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37785,7 +37785,7 @@
       </c>
       <c r="E1384" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37812,7 +37812,7 @@
       </c>
       <c r="E1385" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37839,7 +37839,7 @@
       </c>
       <c r="E1386" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37866,7 +37866,7 @@
       </c>
       <c r="E1387" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37893,7 +37893,7 @@
       </c>
       <c r="E1388" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="E1389" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37947,7 +37947,7 @@
       </c>
       <c r="E1390" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37974,7 +37974,7 @@
       </c>
       <c r="E1391" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38055,7 +38055,7 @@
       </c>
       <c r="E1394" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38082,7 +38082,7 @@
       </c>
       <c r="E1395" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38109,7 +38109,7 @@
       </c>
       <c r="E1396" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38136,7 +38136,7 @@
       </c>
       <c r="E1397" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38163,7 +38163,7 @@
       </c>
       <c r="E1398" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38217,7 +38217,7 @@
       </c>
       <c r="E1400" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38244,7 +38244,7 @@
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38271,7 +38271,7 @@
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38352,7 +38352,7 @@
       </c>
       <c r="E1405" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38379,7 +38379,7 @@
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38406,7 +38406,7 @@
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38433,7 +38433,7 @@
       </c>
       <c r="E1408" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38460,7 +38460,7 @@
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38487,7 +38487,7 @@
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38514,7 +38514,7 @@
       </c>
       <c r="E1411" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38541,7 +38541,7 @@
       </c>
       <c r="E1412" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38568,7 +38568,7 @@
       </c>
       <c r="E1413" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38595,7 +38595,7 @@
       </c>
       <c r="E1414" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38622,7 +38622,7 @@
       </c>
       <c r="E1415" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38649,7 +38649,7 @@
       </c>
       <c r="E1416" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38676,7 +38676,7 @@
       </c>
       <c r="E1417" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38703,7 +38703,7 @@
       </c>
       <c r="E1418" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38730,7 +38730,7 @@
       </c>
       <c r="E1419" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39115,7 +39115,7 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
@@ -39135,14 +39135,14 @@
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
@@ -39162,14 +39162,14 @@
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
@@ -39189,14 +39189,14 @@
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
@@ -39216,14 +39216,14 @@
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
@@ -39243,14 +39243,14 @@
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
@@ -39270,14 +39270,14 @@
       </c>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
@@ -39297,14 +39297,14 @@
       </c>
       <c r="E1440" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
@@ -39324,14 +39324,14 @@
       </c>
       <c r="E1441" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
@@ -39351,14 +39351,14 @@
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
@@ -39378,14 +39378,14 @@
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
@@ -39405,14 +39405,14 @@
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
@@ -39432,14 +39432,14 @@
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
@@ -39459,14 +39459,14 @@
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
@@ -39486,14 +39486,14 @@
       </c>
       <c r="E1447" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
@@ -39513,7 +39513,7 @@
       </c>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -39540,14 +39540,14 @@
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
@@ -39567,14 +39567,14 @@
       </c>
       <c r="E1450" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
@@ -39594,14 +39594,14 @@
       </c>
       <c r="E1451" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
@@ -39621,14 +39621,14 @@
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
@@ -39648,14 +39648,14 @@
       </c>
       <c r="E1453" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
@@ -39675,14 +39675,14 @@
       </c>
       <c r="E1454" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
@@ -39702,7 +39702,7 @@
       </c>
       <c r="E1455" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -39729,14 +39729,14 @@
       </c>
       <c r="E1456" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
@@ -39756,14 +39756,14 @@
       </c>
       <c r="E1457" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
@@ -39783,14 +39783,14 @@
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41079,14 +41079,14 @@
       </c>
       <c r="E1506" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
@@ -41106,14 +41106,14 @@
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -41133,14 +41133,14 @@
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
@@ -41160,7 +41160,7 @@
       </c>
       <c r="E1509" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41187,14 +41187,14 @@
       </c>
       <c r="E1510" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
@@ -41214,14 +41214,14 @@
       </c>
       <c r="E1511" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
@@ -41241,7 +41241,7 @@
       </c>
       <c r="E1512" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41268,14 +41268,14 @@
       </c>
       <c r="E1513" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
@@ -41295,14 +41295,14 @@
       </c>
       <c r="E1514" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="E1515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41349,14 +41349,14 @@
       </c>
       <c r="E1516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
@@ -41376,7 +41376,7 @@
       </c>
       <c r="E1517" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41403,14 +41403,14 @@
       </c>
       <c r="E1518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
@@ -41430,14 +41430,14 @@
       </c>
       <c r="E1519" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
@@ -41457,14 +41457,14 @@
       </c>
       <c r="E1520" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
@@ -41484,7 +41484,7 @@
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41511,14 +41511,14 @@
       </c>
       <c r="E1522" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
@@ -41538,7 +41538,7 @@
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41565,7 +41565,7 @@
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41592,7 +41592,7 @@
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41646,7 +41646,7 @@
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41673,7 +41673,7 @@
       </c>
       <c r="E1528" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41869,7 +41869,7 @@
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
@@ -41889,14 +41889,14 @@
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
@@ -41916,7 +41916,7 @@
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -42031,7 +42031,7 @@
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
@@ -42051,14 +42051,14 @@
       </c>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -42213,7 +42213,7 @@
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42240,7 +42240,7 @@
       </c>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42267,7 +42267,7 @@
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42321,7 +42321,7 @@
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42348,7 +42348,7 @@
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42375,7 +42375,7 @@
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42402,7 +42402,7 @@
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42429,7 +42429,7 @@
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42483,7 +42483,7 @@
       </c>
       <c r="E1558" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42510,7 +42510,7 @@
       </c>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42733,7 +42733,7 @@
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
@@ -42753,14 +42753,14 @@
       </c>
       <c r="E1568" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1569" t="inlineStr">
@@ -42780,14 +42780,14 @@
       </c>
       <c r="E1569" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1570" t="inlineStr">
@@ -42807,14 +42807,14 @@
       </c>
       <c r="E1570" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1571" t="inlineStr">
@@ -42834,14 +42834,14 @@
       </c>
       <c r="E1571" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1572" t="inlineStr">
@@ -42861,14 +42861,14 @@
       </c>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1573" t="inlineStr">
@@ -42888,14 +42888,14 @@
       </c>
       <c r="E1573" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1574" t="inlineStr">
@@ -42915,14 +42915,14 @@
       </c>
       <c r="E1574" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1575" t="inlineStr">
@@ -42942,14 +42942,14 @@
       </c>
       <c r="E1575" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1576" t="inlineStr">
@@ -42969,14 +42969,14 @@
       </c>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1577" t="inlineStr">
@@ -42996,14 +42996,14 @@
       </c>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1578" t="inlineStr">
@@ -43023,14 +43023,14 @@
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1579" t="inlineStr">
@@ -43050,7 +43050,7 @@
       </c>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>

--- a/outputs/alignment-warnings.xlsx
+++ b/outputs/alignment-warnings.xlsx
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -633,14 +633,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -687,14 +687,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -714,14 +714,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -795,14 +795,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -984,14 +984,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1146,14 +1146,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1416,14 +1416,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1578,14 +1578,14 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1686,14 +1686,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1740,14 +1740,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1767,14 +1767,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1794,14 +1794,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7005,14 +7005,14 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7032,14 +7032,14 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7140,14 +7140,14 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7194,14 +7194,14 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9462,14 +9462,14 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -9516,14 +9516,14 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -9543,14 +9543,14 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9570,14 +9570,14 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -9597,14 +9597,14 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -9624,14 +9624,14 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -9651,14 +9651,14 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9678,14 +9678,14 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9705,14 +9705,14 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9732,14 +9732,14 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9759,14 +9759,14 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10029,14 +10029,14 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10056,14 +10056,14 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10083,14 +10083,14 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -10191,14 +10191,14 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -10218,14 +10218,14 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10245,14 +10245,14 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10272,14 +10272,14 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10299,14 +10299,14 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10326,14 +10326,14 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10353,14 +10353,14 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10380,14 +10380,14 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10407,14 +10407,14 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10495,7 +10495,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10515,14 +10515,14 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10542,14 +10542,14 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10569,14 +10569,14 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10596,14 +10596,14 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10623,14 +10623,14 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12108,7 +12108,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13620,7 +13620,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14086,7 +14086,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role S in language: kala1400, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14133,14 +14133,14 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -14160,14 +14160,14 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role S in language: kala1400, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -14187,14 +14187,14 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -14214,14 +14214,14 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -14241,14 +14241,14 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14295,14 +14295,14 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14349,14 +14349,14 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -14376,14 +14376,14 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -14403,14 +14403,14 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14518,7 +14518,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -14538,14 +14538,14 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -14565,14 +14565,14 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -14592,14 +14592,14 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14646,14 +14646,14 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14700,14 +14700,14 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -14727,14 +14727,14 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -14754,14 +14754,14 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15193,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>3pl.ClassA</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15240,14 +15240,14 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>3pl.ClassC</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15294,14 +15294,14 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -15321,14 +15321,14 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -15348,14 +15348,14 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -15375,14 +15375,14 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -15402,14 +15402,14 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>3sg.ClassB</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15456,14 +15456,14 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -15483,14 +15483,14 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -15510,14 +15510,14 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -15537,14 +15537,14 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15591,14 +15591,14 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>3sg.ClassC</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15672,14 +15672,14 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>3pl.ClassA</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -15699,14 +15699,14 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -15726,14 +15726,14 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -15753,14 +15753,14 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -15780,14 +15780,14 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3sg.ClassB</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15834,14 +15834,14 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -15861,14 +15861,14 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -15888,14 +15888,14 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl.ClassC</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15942,14 +15942,14 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -15969,14 +15969,14 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -15996,14 +15996,14 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3sg.ClassC</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16050,14 +16050,14 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -16077,14 +16077,14 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -16104,14 +16104,14 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -16131,14 +16131,14 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17157,7 +17157,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18021,7 +18021,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18615,7 +18615,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18642,7 +18642,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18696,7 +18696,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19101,7 +19101,7 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19128,7 +19128,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19155,7 +19155,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19263,7 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19432,7 +19432,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -19452,14 +19452,14 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -19479,14 +19479,14 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -19506,7 +19506,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19533,14 +19533,14 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -19560,14 +19560,14 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -19587,14 +19587,14 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -19614,14 +19614,14 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -19641,14 +19641,14 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19695,14 +19695,14 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -19722,14 +19722,14 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20073,7 +20073,7 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20181,7 +20181,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20424,7 +20424,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20721,7 +20721,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21261,7 +21261,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21288,7 +21288,7 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21342,7 +21342,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21396,7 +21396,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21423,7 +21423,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21558,7 +21558,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21639,7 +21639,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21693,7 +21693,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21720,7 +21720,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21747,7 +21747,7 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21774,7 +21774,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21828,7 +21828,7 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21990,7 +21990,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22098,7 +22098,7 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22206,14 +22206,14 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -22233,14 +22233,14 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -22260,14 +22260,14 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -22287,14 +22287,14 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -22314,14 +22314,14 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -22341,14 +22341,14 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -22368,14 +22368,14 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -22395,14 +22395,14 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22881,7 +22881,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22935,7 +22935,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23016,7 +23016,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23043,7 +23043,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23124,7 +23124,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23151,7 +23151,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23232,7 +23232,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23313,7 +23313,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23394,7 +23394,7 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23448,7 +23448,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23475,7 +23475,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23610,7 +23610,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23637,7 +23637,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23887,7 +23887,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -23941,7 +23941,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -23961,14 +23961,14 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -23988,7 +23988,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24022,7 +24022,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -24042,14 +24042,14 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -24069,7 +24069,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24103,7 +24103,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -24123,14 +24123,14 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -24150,7 +24150,7 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24184,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -24204,14 +24204,14 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24265,7 +24265,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -24285,14 +24285,14 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -24312,7 +24312,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24346,7 +24346,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -24366,7 +24366,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24447,7 +24447,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24474,7 +24474,7 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24501,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24582,7 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24636,7 +24636,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24690,7 +24690,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24744,7 +24744,7 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24825,7 +24825,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24852,7 +24852,7 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24906,7 +24906,7 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24933,7 +24933,7 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24960,7 +24960,7 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25041,7 +25041,7 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25068,7 +25068,7 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25149,7 +25149,7 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25176,7 +25176,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25230,7 +25230,7 @@
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25338,7 +25338,7 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25446,7 +25446,7 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25500,7 +25500,7 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25554,7 +25554,7 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25608,7 +25608,7 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25770,7 +25770,7 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25797,7 +25797,7 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25824,7 +25824,7 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25905,7 +25905,7 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25986,7 +25986,7 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26013,7 +26013,7 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26094,7 +26094,7 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26148,7 +26148,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26256,7 +26256,7 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26337,7 +26337,7 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26472,7 +26472,7 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26526,7 +26526,7 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26553,7 +26553,7 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26688,7 +26688,7 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27012,7 +27012,7 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27120,7 +27120,7 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27174,7 +27174,7 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27228,7 +27228,7 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27282,7 +27282,7 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27390,7 +27390,7 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27417,7 +27417,7 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27444,7 +27444,7 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27498,7 +27498,7 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27552,7 +27552,7 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27606,7 +27606,7 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27660,7 +27660,7 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27714,7 +27714,7 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27768,7 +27768,7 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27822,7 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27991,7 +27991,7 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
@@ -28011,14 +28011,14 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -28038,14 +28038,14 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
@@ -28065,14 +28065,14 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -28092,14 +28092,14 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
@@ -28119,14 +28119,14 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -28146,7 +28146,7 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28686,7 +28686,7 @@
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28740,7 +28740,7 @@
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28794,7 +28794,7 @@
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28848,7 +28848,7 @@
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30225,7 +30225,7 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30333,7 +30333,7 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30360,7 +30360,7 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30522,7 +30522,7 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30576,7 +30576,7 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30664,7 +30664,7 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
@@ -30684,14 +30684,14 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
@@ -30711,14 +30711,14 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
@@ -30738,14 +30738,14 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
@@ -30765,14 +30765,14 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
@@ -30792,14 +30792,14 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
@@ -30819,14 +30819,14 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
@@ -30846,14 +30846,14 @@
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
@@ -30873,14 +30873,14 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
@@ -30900,14 +30900,14 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
@@ -30927,14 +30927,14 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
@@ -30954,14 +30954,14 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
@@ -30981,7 +30981,7 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -31170,7 +31170,7 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31224,7 +31224,7 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31278,7 +31278,7 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31305,7 +31305,7 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31332,7 +31332,7 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32088,7 +32088,7 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32169,7 +32169,7 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32196,7 +32196,7 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32250,7 +32250,7 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32358,7 +32358,7 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32520,7 +32520,7 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32574,7 +32574,7 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32601,7 +32601,7 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="E1195" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="E1197" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32763,7 +32763,7 @@
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32844,7 +32844,7 @@
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32898,7 +32898,7 @@
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32925,7 +32925,7 @@
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33094,7 +33094,7 @@
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1211" t="inlineStr">
@@ -33114,14 +33114,14 @@
       </c>
       <c r="E1211" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1212" t="inlineStr">
@@ -33141,14 +33141,14 @@
       </c>
       <c r="E1212" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1213" t="inlineStr">
@@ -33168,14 +33168,14 @@
       </c>
       <c r="E1213" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1214" t="inlineStr">
@@ -33195,7 +33195,7 @@
       </c>
       <c r="E1214" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -33256,7 +33256,7 @@
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1217" t="inlineStr">
@@ -33276,14 +33276,14 @@
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1218" t="inlineStr">
@@ -33303,14 +33303,14 @@
       </c>
       <c r="E1218" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1219" t="inlineStr">
@@ -33330,14 +33330,14 @@
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1220" t="inlineStr">
@@ -33357,7 +33357,7 @@
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -33384,7 +33384,7 @@
       </c>
       <c r="E1221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33438,7 +33438,7 @@
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="E1224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="E1225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33519,14 +33519,14 @@
       </c>
       <c r="E1226" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1227" t="inlineStr">
@@ -33546,14 +33546,14 @@
       </c>
       <c r="E1227" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1228" t="inlineStr">
@@ -33573,14 +33573,14 @@
       </c>
       <c r="E1228" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1229" t="inlineStr">
@@ -33600,14 +33600,14 @@
       </c>
       <c r="E1229" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1230" t="inlineStr">
@@ -33627,14 +33627,14 @@
       </c>
       <c r="E1230" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1231" t="inlineStr">
@@ -33654,14 +33654,14 @@
       </c>
       <c r="E1231" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1232" t="inlineStr">
@@ -33681,14 +33681,14 @@
       </c>
       <c r="E1232" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1233" t="inlineStr">
@@ -33708,14 +33708,14 @@
       </c>
       <c r="E1233" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1234" t="inlineStr">
@@ -33735,14 +33735,14 @@
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">
@@ -33762,14 +33762,14 @@
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1236" t="inlineStr">
@@ -33789,7 +33789,7 @@
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -33816,7 +33816,7 @@
       </c>
       <c r="E1237" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33843,14 +33843,14 @@
       </c>
       <c r="E1238" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1239" t="inlineStr">
@@ -33870,14 +33870,14 @@
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1240" t="inlineStr">
@@ -33897,7 +33897,7 @@
       </c>
       <c r="E1240" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -33924,7 +33924,7 @@
       </c>
       <c r="E1241" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33951,7 +33951,7 @@
       </c>
       <c r="E1242" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33978,7 +33978,7 @@
       </c>
       <c r="E1243" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34005,7 +34005,7 @@
       </c>
       <c r="E1244" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="E1245" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34059,7 +34059,7 @@
       </c>
       <c r="E1246" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34086,7 +34086,7 @@
       </c>
       <c r="E1247" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34113,7 +34113,7 @@
       </c>
       <c r="E1248" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34140,7 +34140,7 @@
       </c>
       <c r="E1249" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34167,7 +34167,7 @@
       </c>
       <c r="E1250" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="E1251" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34221,7 +34221,7 @@
       </c>
       <c r="E1252" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34248,7 +34248,7 @@
       </c>
       <c r="E1253" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34275,7 +34275,7 @@
       </c>
       <c r="E1254" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="E1255" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34329,7 +34329,7 @@
       </c>
       <c r="E1256" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34356,7 +34356,7 @@
       </c>
       <c r="E1257" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34383,7 +34383,7 @@
       </c>
       <c r="E1258" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34437,7 +34437,7 @@
       </c>
       <c r="E1260" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34464,7 +34464,7 @@
       </c>
       <c r="E1261" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34518,7 +34518,7 @@
       </c>
       <c r="E1263" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34545,7 +34545,7 @@
       </c>
       <c r="E1264" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34572,7 +34572,7 @@
       </c>
       <c r="E1265" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
       </c>
       <c r="E1267" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
       </c>
       <c r="E1268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34680,7 +34680,7 @@
       </c>
       <c r="E1269" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34707,7 +34707,7 @@
       </c>
       <c r="E1270" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34734,7 +34734,7 @@
       </c>
       <c r="E1271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34761,7 +34761,7 @@
       </c>
       <c r="E1272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34788,7 +34788,7 @@
       </c>
       <c r="E1273" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34842,7 +34842,7 @@
       </c>
       <c r="E1275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="E1276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34896,7 +34896,7 @@
       </c>
       <c r="E1277" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="E1278" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34950,7 +34950,7 @@
       </c>
       <c r="E1279" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34977,7 +34977,7 @@
       </c>
       <c r="E1280" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35004,7 +35004,7 @@
       </c>
       <c r="E1281" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="E1282" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35058,7 +35058,7 @@
       </c>
       <c r="E1283" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35085,7 +35085,7 @@
       </c>
       <c r="E1284" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35193,7 +35193,7 @@
       </c>
       <c r="E1288" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35220,7 +35220,7 @@
       </c>
       <c r="E1289" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35841,7 +35841,7 @@
       </c>
       <c r="E1312" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="E1313" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="E1314" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35922,7 +35922,7 @@
       </c>
       <c r="E1315" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35949,7 +35949,7 @@
       </c>
       <c r="E1316" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35976,7 +35976,7 @@
       </c>
       <c r="E1317" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36003,7 +36003,7 @@
       </c>
       <c r="E1318" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="E1319" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36057,7 +36057,7 @@
       </c>
       <c r="E1320" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36084,7 +36084,7 @@
       </c>
       <c r="E1321" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36111,7 +36111,7 @@
       </c>
       <c r="E1322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36138,7 +36138,7 @@
       </c>
       <c r="E1323" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="E1324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="E1325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36219,7 +36219,7 @@
       </c>
       <c r="E1326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36246,7 +36246,7 @@
       </c>
       <c r="E1327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36273,7 +36273,7 @@
       </c>
       <c r="E1328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36300,7 +36300,7 @@
       </c>
       <c r="E1329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36381,7 +36381,7 @@
       </c>
       <c r="E1332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36408,7 +36408,7 @@
       </c>
       <c r="E1333" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36435,7 +36435,7 @@
       </c>
       <c r="E1334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="E1335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37137,7 +37137,7 @@
       </c>
       <c r="E1360" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37164,7 +37164,7 @@
       </c>
       <c r="E1361" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37191,7 +37191,7 @@
       </c>
       <c r="E1362" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37218,7 +37218,7 @@
       </c>
       <c r="E1363" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37245,7 +37245,7 @@
       </c>
       <c r="E1364" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37272,7 +37272,7 @@
       </c>
       <c r="E1365" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37299,7 +37299,7 @@
       </c>
       <c r="E1366" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37326,7 +37326,7 @@
       </c>
       <c r="E1367" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37353,7 +37353,7 @@
       </c>
       <c r="E1368" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37380,7 +37380,7 @@
       </c>
       <c r="E1369" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="E1370" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37434,7 +37434,7 @@
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="E1389" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37947,7 +37947,7 @@
       </c>
       <c r="E1390" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37974,7 +37974,7 @@
       </c>
       <c r="E1391" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="E1392" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38028,7 +38028,7 @@
       </c>
       <c r="E1393" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38055,7 +38055,7 @@
       </c>
       <c r="E1394" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38082,7 +38082,7 @@
       </c>
       <c r="E1395" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38109,7 +38109,7 @@
       </c>
       <c r="E1396" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38136,7 +38136,7 @@
       </c>
       <c r="E1397" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38163,7 +38163,7 @@
       </c>
       <c r="E1398" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38217,7 +38217,7 @@
       </c>
       <c r="E1400" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38244,7 +38244,7 @@
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38271,7 +38271,7 @@
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38379,7 +38379,7 @@
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38406,7 +38406,7 @@
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38460,7 +38460,7 @@
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38487,7 +38487,7 @@
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38946,7 +38946,7 @@
       </c>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38973,7 +38973,7 @@
       </c>
       <c r="E1428" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39000,7 +39000,7 @@
       </c>
       <c r="E1429" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39027,7 +39027,7 @@
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39054,7 +39054,7 @@
       </c>
       <c r="E1431" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-spec and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39081,7 +39081,7 @@
       </c>
       <c r="E1432" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-generic and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39108,7 +39108,7 @@
       </c>
       <c r="E1433" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-spec and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-spec and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-generic and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39189,7 +39189,7 @@
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39243,7 +39243,7 @@
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-spec and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39412,7 +39412,7 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
@@ -39432,14 +39432,14 @@
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
@@ -39459,14 +39459,14 @@
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
@@ -39486,14 +39486,14 @@
       </c>
       <c r="E1447" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
@@ -39513,14 +39513,14 @@
       </c>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
@@ -39540,14 +39540,14 @@
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
@@ -39567,14 +39567,14 @@
       </c>
       <c r="E1450" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
@@ -39594,7 +39594,7 @@
       </c>
       <c r="E1451" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -39648,14 +39648,14 @@
       </c>
       <c r="E1453" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
@@ -39675,7 +39675,7 @@
       </c>
       <c r="E1454" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39756,7 +39756,7 @@
       </c>
       <c r="E1457" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39783,7 +39783,7 @@
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39810,7 +39810,7 @@
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40222,7 +40222,7 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
@@ -40242,14 +40242,14 @@
       </c>
       <c r="E1475" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="E1476" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -40296,14 +40296,14 @@
       </c>
       <c r="E1477" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
@@ -40323,14 +40323,14 @@
       </c>
       <c r="E1478" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
@@ -40350,14 +40350,14 @@
       </c>
       <c r="E1479" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="E1480" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -40404,14 +40404,14 @@
       </c>
       <c r="E1481" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
@@ -40431,7 +40431,7 @@
       </c>
       <c r="E1482" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -41052,7 +41052,7 @@
       </c>
       <c r="E1505" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41079,7 +41079,7 @@
       </c>
       <c r="E1506" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41106,7 +41106,7 @@
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41133,7 +41133,7 @@
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41376,7 +41376,7 @@
       </c>
       <c r="E1517" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41403,7 +41403,7 @@
       </c>
       <c r="E1518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41430,7 +41430,7 @@
       </c>
       <c r="E1519" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41457,7 +41457,7 @@
       </c>
       <c r="E1520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41484,7 +41484,7 @@
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41511,7 +41511,7 @@
       </c>
       <c r="E1522" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41538,7 +41538,7 @@
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41565,7 +41565,7 @@
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41592,7 +41592,7 @@
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41619,7 +41619,7 @@
       </c>
       <c r="E1526" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41646,7 +41646,7 @@
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41673,7 +41673,7 @@
       </c>
       <c r="E1528" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41862,7 +41862,7 @@
       </c>
       <c r="E1535" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41889,7 +41889,7 @@
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41916,7 +41916,7 @@
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41943,7 +41943,7 @@
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41970,7 +41970,7 @@
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41997,7 +41997,7 @@
       </c>
       <c r="E1540" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42051,7 +42051,7 @@
       </c>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42078,7 +42078,7 @@
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42105,7 +42105,7 @@
       </c>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42132,7 +42132,7 @@
       </c>
       <c r="E1545" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42186,7 +42186,7 @@
       </c>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42213,7 +42213,7 @@
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42240,7 +42240,7 @@
       </c>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42267,7 +42267,7 @@
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42294,7 +42294,7 @@
       </c>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42321,7 +42321,7 @@
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42348,7 +42348,7 @@
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42375,7 +42375,7 @@
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42402,7 +42402,7 @@
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42429,7 +42429,7 @@
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42456,7 +42456,7 @@
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42672,7 +42672,7 @@
       </c>
       <c r="E1565" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42699,7 +42699,7 @@
       </c>
       <c r="E1566" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42726,7 +42726,7 @@
       </c>
       <c r="E1567" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42753,7 +42753,7 @@
       </c>
       <c r="E1568" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42942,7 +42942,7 @@
       </c>
       <c r="E1575" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42969,7 +42969,7 @@
       </c>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42996,7 +42996,7 @@
       </c>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43023,7 +43023,7 @@
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43050,7 +43050,7 @@
       </c>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43077,7 +43077,7 @@
       </c>
       <c r="E1580" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43104,7 +43104,7 @@
       </c>
       <c r="E1581" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43131,7 +43131,7 @@
       </c>
       <c r="E1582" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43158,7 +43158,7 @@
       </c>
       <c r="E1583" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43185,7 +43185,7 @@
       </c>
       <c r="E1584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43212,7 +43212,7 @@
       </c>
       <c r="E1585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="E1586" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43266,7 +43266,7 @@
       </c>
       <c r="E1587" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43293,7 +43293,7 @@
       </c>
       <c r="E1588" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>

--- a/outputs/alignment-warnings.xlsx
+++ b/outputs/alignment-warnings.xlsx
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -633,14 +633,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -660,14 +660,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -687,14 +687,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -714,14 +714,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -849,14 +849,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -876,14 +876,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -903,14 +903,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -930,14 +930,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -957,14 +957,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -984,14 +984,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1092,14 +1092,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1119,14 +1119,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1308,14 +1308,14 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1335,14 +1335,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1362,14 +1362,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1416,14 +1416,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1443,14 +1443,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1524,14 +1524,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1740,14 +1740,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1767,14 +1767,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1794,14 +1794,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3fobv-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3fobv-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3fobv-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3fobv-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -6978,14 +6978,14 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7005,14 +7005,14 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7032,14 +7032,14 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7059,14 +7059,14 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7086,14 +7086,14 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7113,14 +7113,14 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7167,14 +7167,14 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7194,14 +7194,14 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7248,14 +7248,14 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7275,14 +7275,14 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9462,14 +9462,14 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -9543,14 +9543,14 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9570,14 +9570,14 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -9597,14 +9597,14 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -9624,14 +9624,14 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -9651,14 +9651,14 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -9705,14 +9705,14 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9732,14 +9732,14 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9759,14 +9759,14 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10063,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10083,14 +10083,14 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10110,14 +10110,14 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -10137,14 +10137,14 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -10164,14 +10164,14 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -10191,14 +10191,14 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -10218,14 +10218,14 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10245,14 +10245,14 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10272,14 +10272,14 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10387,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10407,14 +10407,14 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10434,14 +10434,14 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10461,14 +10461,14 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10488,14 +10488,14 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10515,14 +10515,14 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10542,14 +10542,14 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10569,14 +10569,14 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10596,14 +10596,14 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13620,7 +13620,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14086,7 +14086,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role S in language: kala1400, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14133,14 +14133,14 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -14160,14 +14160,14 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role S in language: kala1400, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -14187,14 +14187,14 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -14214,14 +14214,14 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -14241,14 +14241,14 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14295,14 +14295,14 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14376,14 +14376,14 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -14403,14 +14403,14 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14464,7 +14464,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14511,14 +14511,14 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -14538,14 +14538,14 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -14565,14 +14565,14 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -14592,14 +14592,14 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14646,14 +14646,14 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14727,14 +14727,14 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -14754,14 +14754,14 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14815,7 +14815,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15240,7 +15240,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15348,7 +15348,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15672,14 +15672,14 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>3pl.ClassA</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -15699,14 +15699,14 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15753,14 +15753,14 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -15780,14 +15780,14 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>3sg.ClassB</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -15807,14 +15807,14 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -15834,14 +15834,14 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -15861,14 +15861,14 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>3sg.ClassC</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -15888,14 +15888,14 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>3pl.ClassC</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -15915,14 +15915,14 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl.ClassC</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -15942,14 +15942,14 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -15969,14 +15969,14 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -15996,14 +15996,14 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>3sg.ClassC</t>
+          <t>3sg.ClassB</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16050,14 +16050,14 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -16077,14 +16077,14 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16165,7 +16165,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl.ClassA</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17157,7 +17157,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18021,7 +18021,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18210,7 +18210,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18615,7 +18615,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19155,7 +19155,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19432,7 +19432,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -19452,14 +19452,14 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -19479,14 +19479,14 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -19506,14 +19506,14 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19594,7 +19594,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -19614,14 +19614,14 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -19641,14 +19641,14 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -19668,14 +19668,14 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19803,7 +19803,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19911,7 +19911,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20019,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20424,7 +20424,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20586,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21558,7 +21558,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21720,7 +21720,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22206,7 +22206,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22240,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -22260,14 +22260,14 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -22287,14 +22287,14 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -22348,7 +22348,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -22368,14 +22368,14 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -22395,14 +22395,14 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -22827,7 +22827,7 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22881,7 +22881,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22935,7 +22935,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22962,7 +22962,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23016,7 +23016,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23043,7 +23043,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23124,7 +23124,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23151,7 +23151,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23448,7 +23448,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23502,7 +23502,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23529,7 +23529,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23610,7 +23610,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23691,7 +23691,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23887,7 +23887,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23995,7 +23995,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -24015,7 +24015,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24042,14 +24042,14 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -24069,7 +24069,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24123,7 +24123,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24157,7 +24157,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24204,14 +24204,14 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24285,7 +24285,7 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24319,7 +24319,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24366,7 +24366,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24420,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24447,7 +24447,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24474,7 +24474,7 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24501,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24582,7 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24636,7 +24636,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24690,7 +24690,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24744,7 +24744,7 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24933,7 +24933,7 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24960,7 +24960,7 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25149,7 +25149,7 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25176,7 +25176,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25338,7 +25338,7 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25365,7 +25365,7 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25446,7 +25446,7 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25500,7 +25500,7 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25554,7 +25554,7 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25608,7 +25608,7 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25770,7 +25770,7 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25797,7 +25797,7 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25824,7 +25824,7 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25986,7 +25986,7 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26013,7 +26013,7 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26094,7 +26094,7 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26148,7 +26148,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26202,7 +26202,7 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26256,7 +26256,7 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26418,7 +26418,7 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26472,7 +26472,7 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26526,7 +26526,7 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26553,7 +26553,7 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27012,7 +27012,7 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27066,7 +27066,7 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27120,7 +27120,7 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27174,7 +27174,7 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27228,7 +27228,7 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27282,7 +27282,7 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27390,7 +27390,7 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27417,7 +27417,7 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27444,7 +27444,7 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27498,7 +27498,7 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27552,7 +27552,7 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27633,7 +27633,7 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27714,7 +27714,7 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27930,7 +27930,7 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27957,7 +27957,7 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27984,14 +27984,14 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
@@ -28011,7 +28011,7 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -28045,7 +28045,7 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
@@ -28065,14 +28065,14 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -28092,7 +28092,7 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -28126,7 +28126,7 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -28146,7 +28146,7 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28740,7 +28740,7 @@
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28821,7 +28821,7 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30333,14 +30333,14 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
@@ -30360,14 +30360,14 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
@@ -30387,7 +30387,7 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30441,7 +30441,7 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30522,7 +30522,7 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30576,14 +30576,14 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B1118" t="inlineStr">
@@ -30603,14 +30603,14 @@
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30691,7 +30691,7 @@
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
@@ -30711,14 +30711,14 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
@@ -30738,14 +30738,14 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
@@ -30765,14 +30765,14 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
@@ -30792,14 +30792,14 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -30853,7 +30853,7 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
@@ -30873,14 +30873,14 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
@@ -30900,14 +30900,14 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
@@ -30927,14 +30927,14 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
@@ -30954,14 +30954,14 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
@@ -30981,7 +30981,7 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -31170,7 +31170,7 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31224,7 +31224,7 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31278,7 +31278,7 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31305,7 +31305,7 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31332,7 +31332,7 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32088,7 +32088,7 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32142,7 +32142,7 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32196,7 +32196,7 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32250,7 +32250,7 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32304,7 +32304,7 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32358,7 +32358,7 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33094,7 +33094,7 @@
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1211" t="inlineStr">
@@ -33114,14 +33114,14 @@
       </c>
       <c r="E1211" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1212" t="inlineStr">
@@ -33141,14 +33141,14 @@
       </c>
       <c r="E1212" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1213" t="inlineStr">
@@ -33168,14 +33168,14 @@
       </c>
       <c r="E1213" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1214" t="inlineStr">
@@ -33195,14 +33195,14 @@
       </c>
       <c r="E1214" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1215" t="inlineStr">
@@ -33222,14 +33222,14 @@
       </c>
       <c r="E1215" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1216" t="inlineStr">
@@ -33249,14 +33249,14 @@
       </c>
       <c r="E1216" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1217" t="inlineStr">
@@ -33276,14 +33276,14 @@
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1218" t="inlineStr">
@@ -33303,14 +33303,14 @@
       </c>
       <c r="E1218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1219" t="inlineStr">
@@ -33330,14 +33330,14 @@
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1220" t="inlineStr">
@@ -33357,14 +33357,14 @@
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1221" t="inlineStr">
@@ -33384,14 +33384,14 @@
       </c>
       <c r="E1221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1222" t="inlineStr">
@@ -33411,7 +33411,7 @@
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -33438,7 +33438,7 @@
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33465,14 +33465,14 @@
       </c>
       <c r="E1224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1225" t="inlineStr">
@@ -33492,14 +33492,14 @@
       </c>
       <c r="E1225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1226" t="inlineStr">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="E1226" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="E1227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33600,7 +33600,7 @@
       </c>
       <c r="E1229" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33627,14 +33627,14 @@
       </c>
       <c r="E1230" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1231" t="inlineStr">
@@ -33654,14 +33654,14 @@
       </c>
       <c r="E1231" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1232" t="inlineStr">
@@ -33681,14 +33681,14 @@
       </c>
       <c r="E1232" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1233" t="inlineStr">
@@ -33708,14 +33708,14 @@
       </c>
       <c r="E1233" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B1234" t="inlineStr">
@@ -33735,14 +33735,14 @@
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">
@@ -33762,14 +33762,14 @@
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1236" t="inlineStr">
@@ -33789,14 +33789,14 @@
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1237" t="inlineStr">
@@ -33816,14 +33816,14 @@
       </c>
       <c r="E1237" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1238" t="inlineStr">
@@ -33843,14 +33843,14 @@
       </c>
       <c r="E1238" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1239" t="inlineStr">
@@ -33870,14 +33870,14 @@
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1240" t="inlineStr">
@@ -33897,14 +33897,14 @@
       </c>
       <c r="E1240" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1241" t="inlineStr">
@@ -33924,14 +33924,14 @@
       </c>
       <c r="E1241" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B1242" t="inlineStr">
@@ -33951,7 +33951,7 @@
       </c>
       <c r="E1242" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: nucl1302, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -33978,7 +33978,7 @@
       </c>
       <c r="E1243" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34005,7 +34005,7 @@
       </c>
       <c r="E1244" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34086,7 +34086,7 @@
       </c>
       <c r="E1247" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34113,7 +34113,7 @@
       </c>
       <c r="E1248" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34275,7 +34275,7 @@
       </c>
       <c r="E1254" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="E1255" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34383,7 +34383,7 @@
       </c>
       <c r="E1258" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="E1259" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34437,7 +34437,7 @@
       </c>
       <c r="E1260" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34464,7 +34464,7 @@
       </c>
       <c r="E1261" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="E1262" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34518,7 +34518,7 @@
       </c>
       <c r="E1263" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34545,7 +34545,7 @@
       </c>
       <c r="E1264" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34599,7 +34599,7 @@
       </c>
       <c r="E1266" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
       </c>
       <c r="E1267" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
       </c>
       <c r="E1268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34680,7 +34680,7 @@
       </c>
       <c r="E1269" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34707,7 +34707,7 @@
       </c>
       <c r="E1270" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34734,7 +34734,7 @@
       </c>
       <c r="E1271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34761,7 +34761,7 @@
       </c>
       <c r="E1272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="E1274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34842,7 +34842,7 @@
       </c>
       <c r="E1275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="E1276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34896,7 +34896,7 @@
       </c>
       <c r="E1277" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="E1278" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34950,7 +34950,7 @@
       </c>
       <c r="E1279" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34977,7 +34977,7 @@
       </c>
       <c r="E1280" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35004,7 +35004,7 @@
       </c>
       <c r="E1281" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="E1282" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35058,7 +35058,7 @@
       </c>
       <c r="E1283" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35085,7 +35085,7 @@
       </c>
       <c r="E1284" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35112,7 +35112,7 @@
       </c>
       <c r="E1285" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35139,7 +35139,7 @@
       </c>
       <c r="E1286" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35166,7 +35166,7 @@
       </c>
       <c r="E1287" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35193,7 +35193,7 @@
       </c>
       <c r="E1288" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35220,7 +35220,7 @@
       </c>
       <c r="E1289" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35841,7 +35841,7 @@
       </c>
       <c r="E1312" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="E1313" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="E1314" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35922,7 +35922,7 @@
       </c>
       <c r="E1315" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35949,7 +35949,7 @@
       </c>
       <c r="E1316" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35976,7 +35976,7 @@
       </c>
       <c r="E1317" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36003,7 +36003,7 @@
       </c>
       <c r="E1318" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="E1319" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36057,7 +36057,7 @@
       </c>
       <c r="E1320" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36084,7 +36084,7 @@
       </c>
       <c r="E1321" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36111,7 +36111,7 @@
       </c>
       <c r="E1322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36138,7 +36138,7 @@
       </c>
       <c r="E1323" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="E1324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="E1325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36219,7 +36219,7 @@
       </c>
       <c r="E1326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36246,7 +36246,7 @@
       </c>
       <c r="E1327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36273,7 +36273,7 @@
       </c>
       <c r="E1328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36300,7 +36300,7 @@
       </c>
       <c r="E1329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36381,7 +36381,7 @@
       </c>
       <c r="E1332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36408,7 +36408,7 @@
       </c>
       <c r="E1333" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36435,7 +36435,7 @@
       </c>
       <c r="E1334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="E1335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37191,7 +37191,7 @@
       </c>
       <c r="E1362" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37218,7 +37218,7 @@
       </c>
       <c r="E1363" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37245,7 +37245,7 @@
       </c>
       <c r="E1364" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37272,7 +37272,7 @@
       </c>
       <c r="E1365" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37353,7 +37353,7 @@
       </c>
       <c r="E1368" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37380,7 +37380,7 @@
       </c>
       <c r="E1369" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="E1370" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37434,7 +37434,7 @@
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37738,7 +37738,7 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
@@ -37758,14 +37758,14 @@
       </c>
       <c r="E1383" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: nort2980, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
@@ -37785,14 +37785,14 @@
       </c>
       <c r="E1384" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: nort2980, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
@@ -37812,14 +37812,14 @@
       </c>
       <c r="E1385" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: nort2980, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="E1386" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: nort2980, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="E1389" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37947,7 +37947,7 @@
       </c>
       <c r="E1390" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37974,7 +37974,7 @@
       </c>
       <c r="E1391" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="E1392" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38028,7 +38028,7 @@
       </c>
       <c r="E1393" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38055,7 +38055,7 @@
       </c>
       <c r="E1394" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38082,7 +38082,7 @@
       </c>
       <c r="E1395" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38109,7 +38109,7 @@
       </c>
       <c r="E1396" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38136,7 +38136,7 @@
       </c>
       <c r="E1397" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38163,7 +38163,7 @@
       </c>
       <c r="E1398" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38217,7 +38217,7 @@
       </c>
       <c r="E1400" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38244,7 +38244,7 @@
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38271,7 +38271,7 @@
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38946,7 +38946,7 @@
       </c>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39000,7 +39000,7 @@
       </c>
       <c r="E1429" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39027,7 +39027,7 @@
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39054,7 +39054,7 @@
       </c>
       <c r="E1431" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-generic and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39081,7 +39081,7 @@
       </c>
       <c r="E1432" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-generic and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-spec and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39108,7 +39108,7 @@
       </c>
       <c r="E1433" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-spec and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39189,7 +39189,7 @@
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-spec and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39216,7 +39216,7 @@
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-generic and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39243,7 +39243,7 @@
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-spec and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-generic and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39412,7 +39412,7 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
@@ -39486,14 +39486,14 @@
       </c>
       <c r="E1447" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
@@ -39513,7 +39513,7 @@
       </c>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39567,7 +39567,7 @@
       </c>
       <c r="E1450" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39601,7 +39601,7 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
@@ -39621,14 +39621,14 @@
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
@@ -39648,14 +39648,14 @@
       </c>
       <c r="E1453" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
@@ -39675,7 +39675,7 @@
       </c>
       <c r="E1454" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -40222,7 +40222,7 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
@@ -40242,7 +40242,7 @@
       </c>
       <c r="E1475" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -40269,14 +40269,14 @@
       </c>
       <c r="E1476" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
@@ -40296,14 +40296,14 @@
       </c>
       <c r="E1477" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
@@ -40323,14 +40323,14 @@
       </c>
       <c r="E1478" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="E1479" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -40377,14 +40377,14 @@
       </c>
       <c r="E1480" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
@@ -40404,14 +40404,14 @@
       </c>
       <c r="E1481" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
@@ -40431,7 +40431,7 @@
       </c>
       <c r="E1482" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -40998,7 +40998,7 @@
       </c>
       <c r="E1503" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41025,7 +41025,7 @@
       </c>
       <c r="E1504" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41052,7 +41052,7 @@
       </c>
       <c r="E1505" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41079,7 +41079,7 @@
       </c>
       <c r="E1506" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41106,7 +41106,7 @@
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41133,7 +41133,7 @@
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41376,7 +41376,7 @@
       </c>
       <c r="E1517" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41403,7 +41403,7 @@
       </c>
       <c r="E1518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41430,7 +41430,7 @@
       </c>
       <c r="E1519" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41457,7 +41457,7 @@
       </c>
       <c r="E1520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41484,7 +41484,7 @@
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41511,7 +41511,7 @@
       </c>
       <c r="E1522" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41538,7 +41538,7 @@
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41565,7 +41565,7 @@
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41592,7 +41592,7 @@
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41619,7 +41619,7 @@
       </c>
       <c r="E1526" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41646,7 +41646,7 @@
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41673,7 +41673,7 @@
       </c>
       <c r="E1528" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41862,7 +41862,7 @@
       </c>
       <c r="E1535" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41889,7 +41889,7 @@
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41916,7 +41916,7 @@
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41943,7 +41943,7 @@
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -41997,7 +41997,7 @@
       </c>
       <c r="E1540" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42051,7 +42051,7 @@
       </c>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42078,7 +42078,7 @@
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42105,7 +42105,7 @@
       </c>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42132,7 +42132,7 @@
       </c>
       <c r="E1545" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42159,7 +42159,7 @@
       </c>
       <c r="E1546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42186,7 +42186,7 @@
       </c>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42213,7 +42213,7 @@
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42240,7 +42240,7 @@
       </c>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42267,7 +42267,7 @@
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42321,7 +42321,7 @@
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42348,7 +42348,7 @@
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42375,7 +42375,7 @@
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42402,7 +42402,7 @@
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42429,7 +42429,7 @@
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42456,7 +42456,7 @@
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42483,7 +42483,7 @@
       </c>
       <c r="E1558" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42672,7 +42672,7 @@
       </c>
       <c r="E1565" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42699,7 +42699,7 @@
       </c>
       <c r="E1566" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42726,7 +42726,7 @@
       </c>
       <c r="E1567" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42753,7 +42753,7 @@
       </c>
       <c r="E1568" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42942,7 +42942,7 @@
       </c>
       <c r="E1575" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42969,7 +42969,7 @@
       </c>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -42996,7 +42996,7 @@
       </c>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43023,7 +43023,7 @@
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43050,7 +43050,7 @@
       </c>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43077,7 +43077,7 @@
       </c>
       <c r="E1580" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43104,7 +43104,7 @@
       </c>
       <c r="E1581" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43131,7 +43131,7 @@
       </c>
       <c r="E1582" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43158,7 +43158,7 @@
       </c>
       <c r="E1583" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43185,7 +43185,7 @@
       </c>
       <c r="E1584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43212,7 +43212,7 @@
       </c>
       <c r="E1585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="E1586" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43266,7 +43266,7 @@
       </c>
       <c r="E1587" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -43293,7 +43293,7 @@
       </c>
       <c r="E1588" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>

--- a/outputs/alignment-warnings.xlsx
+++ b/outputs/alignment-warnings.xlsx
@@ -721,7 +721,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -768,14 +768,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -795,14 +795,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -822,14 +822,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -849,14 +849,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1119,14 +1119,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1254,14 +1254,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1du</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: cams1241, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1740,14 +1740,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6978,14 +6978,14 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7005,14 +7005,14 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7032,14 +7032,14 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7059,14 +7059,14 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7086,14 +7086,14 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7113,14 +7113,14 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7140,14 +7140,14 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7167,14 +7167,14 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7194,14 +7194,14 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7248,14 +7248,14 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7275,14 +7275,14 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -9516,14 +9516,14 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -9543,14 +9543,14 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9570,14 +9570,14 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -9597,14 +9597,14 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9678,14 +9678,14 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9705,14 +9705,14 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9732,14 +9732,14 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9759,14 +9759,14 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yana1271, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10029,14 +10029,14 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10056,14 +10056,14 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10083,14 +10083,14 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10110,14 +10110,14 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -10137,14 +10137,14 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10225,7 +10225,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10245,14 +10245,14 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10272,14 +10272,14 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10299,14 +10299,14 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10326,14 +10326,14 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10353,14 +10353,14 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10380,14 +10380,14 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10407,14 +10407,14 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10434,14 +10434,14 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10461,14 +10461,14 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10549,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10569,14 +10569,14 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10596,14 +10596,14 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10623,14 +10623,14 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12108,7 +12108,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13620,7 +13620,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14086,7 +14086,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role S in language: kala1400, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14133,14 +14133,14 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role S in language: kala1400, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14187,14 +14187,14 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14241,14 +14241,14 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14295,14 +14295,14 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14349,14 +14349,14 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -14376,14 +14376,14 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -14403,14 +14403,14 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -14430,14 +14430,14 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -14457,14 +14457,14 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14538,14 +14538,14 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14592,14 +14592,14 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14646,14 +14646,14 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -14700,14 +14700,14 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -14727,14 +14727,14 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -14754,14 +14754,14 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -14781,14 +14781,14 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -14808,14 +14808,14 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15213,14 +15213,14 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3sg.ClassB</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15274,7 +15274,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -15294,14 +15294,14 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -15321,14 +15321,14 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -15348,14 +15348,14 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15402,14 +15402,14 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl.ClassA</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15456,14 +15456,14 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3sg.ClassC</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15510,14 +15510,14 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -15537,14 +15537,14 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -15564,14 +15564,14 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>3pl.ClassC</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15618,14 +15618,14 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -15645,14 +15645,14 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -15672,14 +15672,14 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15726,14 +15726,14 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -15753,14 +15753,14 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -15780,14 +15780,14 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -15807,14 +15807,14 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -15834,14 +15834,14 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -15861,14 +15861,14 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>3sg.ClassC</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15915,14 +15915,14 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>3pl.ClassC</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassC and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15996,14 +15996,14 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>3sg.ClassB</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3sg.ClassB and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16050,14 +16050,14 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -16077,14 +16077,14 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -16104,14 +16104,14 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -16131,14 +16131,14 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -16158,14 +16158,14 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>3pl.ClassA</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl.ClassA and role A in language: kiow1266, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17157,7 +17157,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18021,7 +18021,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18615,7 +18615,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19432,7 +19432,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -19452,14 +19452,14 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -19479,14 +19479,14 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -19506,14 +19506,14 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -19533,14 +19533,14 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -19560,14 +19560,14 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -19587,14 +19587,14 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -19614,14 +19614,14 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -19641,14 +19641,14 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -19668,14 +19668,14 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -19695,14 +19695,14 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -19722,14 +19722,14 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19803,7 +19803,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19911,7 +19911,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20019,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20073,7 +20073,7 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20181,7 +20181,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20424,7 +20424,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20586,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20721,7 +20721,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21423,7 +21423,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21558,7 +21558,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21639,7 +21639,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21693,7 +21693,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21747,7 +21747,7 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21774,7 +21774,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21828,7 +21828,7 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21990,7 +21990,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22098,7 +22098,7 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22206,14 +22206,14 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -22233,14 +22233,14 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -22314,14 +22314,14 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -22341,14 +22341,14 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -22402,7 +22402,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -22827,7 +22827,7 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22881,7 +22881,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22935,7 +22935,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23016,7 +23016,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23043,7 +23043,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23151,7 +23151,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23232,7 +23232,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23313,7 +23313,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23394,7 +23394,7 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23448,7 +23448,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23502,7 +23502,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23610,7 +23610,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23907,7 +23907,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23934,14 +23934,14 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -23961,14 +23961,14 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -23988,14 +23988,14 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -24015,7 +24015,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24069,7 +24069,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24096,14 +24096,14 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -24123,14 +24123,14 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -24150,14 +24150,14 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24231,7 +24231,7 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24258,14 +24258,14 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -24285,14 +24285,14 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -24312,14 +24312,14 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24636,7 +24636,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24690,7 +24690,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25041,7 +25041,7 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25068,7 +25068,7 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25149,7 +25149,7 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25176,7 +25176,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25365,7 +25365,7 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25392,7 +25392,7 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25446,7 +25446,7 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25500,7 +25500,7 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25797,7 +25797,7 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25824,7 +25824,7 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25905,7 +25905,7 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25986,7 +25986,7 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26013,7 +26013,7 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26094,7 +26094,7 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26148,7 +26148,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26418,7 +26418,7 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26526,7 +26526,7 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26553,7 +26553,7 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26688,7 +26688,7 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26904,7 +26904,7 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_N